--- a/data/reports/viral_posts.xlsx
+++ b/data/reports/viral_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,112 +477,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>post_id</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>image_urls</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>bike storage tent</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>27800</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1700</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://facebook.com/groups/123/posts/987654321</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Using a bike storage shed as an outdoor kitchen or storage space while camping. Solved all our morning coffee problems!</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Lucas Ethan</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>987654321</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://images.unsplash.com/photo-1504280390367-361c6d9f38f4?w=600</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rv cushion covers</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>350</v>
-      </c>
-      <c r="C3" t="n">
-        <v>42</v>
-      </c>
-      <c r="D3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://facebook.com/groups/123/posts/123456789</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Way cheaper than replacing the cushions, and when they get dirty, I just throw them in the wash! Best update to our 20-year RV dinette.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sarah Connor</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>123456789</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://images.unsplash.com/photo-1523755230320-71a657dcdd76?w=600</t>
         </is>
       </c>
     </row>

--- a/data/reports/viral_posts.xlsx
+++ b/data/reports/viral_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,1946 @@
           <t>post_id</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>image_urls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>492</v>
+      </c>
+      <c r="C2" t="n">
+        <v>69</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/2389439124523226/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>17 weeks of hard work- but our total transformation is done! ...well mostly done 
+We are so happy!!</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>data\images\hack_2389439124523226\img_1.jpg; data\images\hack_2389439124523226\img_2.jpg; data\images\hack_2389439124523226\img_3.jpg; data\images\hack_2389439124523226\img_4.jpg; data\images\hack_2389439124523226\img_5.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2389439124523226</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>492</v>
+      </c>
+      <c r="C3" t="n">
+        <v>69</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/2389439124523226/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>17 weeks of hard work- but our total transformation is done! ...well mostly done 
+We are so happy!!</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>data\images\hack_2389439124523226\img_1.jpg; data\images\hack_2389439124523226\img_2.jpg; data\images\hack_2389439124523226\img_3.jpg; data\images\hack_2389439124523226\img_4.jpg; data\images\hack_2389439124523226\img_5.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2389439124523226</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>377</v>
+      </c>
+      <c r="C4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3308082032658926/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Our camper didn’t come with a ladder to the upper bunks. My girls struggle to climb up to them to play. So I wanted a ladder but not too tall. I ended up getting a trampoline ladder. It cost only $25 and just hooked onto the bunk</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>data\images\hack_3308082032658926\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3308082032658926</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>377</v>
+      </c>
+      <c r="C5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3308082032658926/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Our camper didn’t come with a ladder to the upper bunks. My girls struggle to climb up to them to play. So I wanted a ladder but not too tall. I ended up getting a trampoline ladder. It cost only $25 and just hooked onto the bunk</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>data\images\hack_3308082032658926\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>3308082032658926</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>127</v>
+      </c>
+      <c r="C6" t="n">
+        <v>326</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3353573731443089/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Any ideas on how to not get your camper to shake? I have not been able to sleep at all because I literally feel the kids move in their sleep.  We bought the x jack to help but it’s still not working.  Any suggestions!</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>data\images\hack_3353573731443089\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3353573731443089</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>127</v>
+      </c>
+      <c r="C7" t="n">
+        <v>326</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3353573731443089/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Any ideas on how to not get your camper to shake? I have not been able to sleep at all because I literally feel the kids move in their sleep.  We bought the x jack to help but it’s still not working.  Any suggestions!</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>data\images\hack_3353573731443089\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3353573731443089</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>124</v>
+      </c>
+      <c r="C8" t="n">
+        <v>343</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3845725655561225/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3845725655561225</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>124</v>
+      </c>
+      <c r="C9" t="n">
+        <v>343</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3845725655561225/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3845725655561225</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>80</v>
+      </c>
+      <c r="C10" t="n">
+        <v>92</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3583318008493819/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>It's level, but still wobbles when walking inside.
+Can you knowledgeable friends tell me what you think of our set up. We've heard that not lowering the stabilizers all the way helps with the wobble.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>data\images\hack_3583318008493819\img_1.jpg; data\images\hack_3583318008493819\img_2.jpg; data\images\hack_3583318008493819\img_3.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3583318008493819</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/763072132_10240527915834058_262860686266165320_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tQPKb_7z3scQ7kNvwHI1W7g&amp;_nc_oc=AdryOCOHLUetXqxLh_YB0dln50lhK5trI90T_Fm1qocc_zcSjKjM7rFYwajXvgsjhTI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJ0GnPf57poAwnS1tveFqIifG41xCwgcTXoj7nwXsPD0g&amp;oe=6AB39330; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/764719882_10240527916554076_6179174592261675065_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGePznIup-IQ7kNvwF8n1gs&amp;_nc_oc=AdpGktVoydqk0AxdQDAOzbx_Pf2MDjo3DIQObD1Zjm6Y7VQBbann44VUTt2JZv16NT8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJvlQLTekeLpX0VeuXsY7AW8BTlFEb4ontl07T28WmncA&amp;oe=6AB39768; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/762276276_10240527918834133_6935526286052437077_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=LUYt4ZPtFlQQ7kNvwFtDGTf&amp;_nc_oc=Ados7w7e5WTUF89zeazhrONFUSOjfR3KkU-WEt4FzNzv3RCM9gJpPLl89FV5RIzy0P4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQIUbRAOYKraspj5sBL0vF-0I_3MUiK5eLiusqFF-B6VQQ&amp;oe=6AB3908B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C11" t="n">
+        <v>92</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3583318008493819/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>It's level, but still wobbles when walking inside.
+Can you knowledgeable friends tell me what you think of our set up. We've heard that not lowering the stabilizers all the way helps with the wobble.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>data\images\hack_3583318008493819\img_1.jpg; data\images\hack_3583318008493819\img_2.jpg; data\images\hack_3583318008493819\img_3.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3583318008493819</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/763072132_10240527915834058_262860686266165320_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tQPKb_7z3scQ7kNvwHI1W7g&amp;_nc_oc=AdryOCOHLUetXqxLh_YB0dln50lhK5trI90T_Fm1qocc_zcSjKjM7rFYwajXvgsjhTI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJ0GnPf57poAwnS1tveFqIifG41xCwgcTXoj7nwXsPD0g&amp;oe=6AB39330; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/764719882_10240527916554076_6179174592261675065_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGePznIup-IQ7kNvwF8n1gs&amp;_nc_oc=AdpGktVoydqk0AxdQDAOzbx_Pf2MDjo3DIQObD1Zjm6Y7VQBbann44VUTt2JZv16NT8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJvlQLTekeLpX0VeuXsY7AW8BTlFEb4ontl07T28WmncA&amp;oe=6AB39768; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/762276276_10240527918834133_6935526286052437077_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=LUYt4ZPtFlQQ7kNvwFtDGTf&amp;_nc_oc=Ados7w7e5WTUF89zeazhrONFUSOjfR3KkU-WEt4FzNzv3RCM9gJpPLl89FV5RIzy0P4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQIUbRAOYKraspj5sBL0vF-0I_3MUiK5eLiusqFF-B6VQQ&amp;oe=6AB3908B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>54</v>
+      </c>
+      <c r="C12" t="n">
+        <v>69</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3513687305456890/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hello everybody! 
+New, full time rv living here! 
+We live in Texas and this heat is getting to us 
+With all 3 ac running it stays about 74 in the camper, which is fine. But hits up to 80 in the bedroom. What's yalls best tips and tricks to keeping the heat down without frying our ac units? 
+We have dehumidifiers, keep the window shades down and the windows are factory tinted (we will be putting darker tint on the windows soon). ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>data\images\hack_3513687305456890\img_1.jpg; data\images\hack_3513687305456890\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3513687305456890</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>54</v>
+      </c>
+      <c r="C13" t="n">
+        <v>69</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3513687305456890/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hello everybody! 
+New, full time rv living here! 
+We live in Texas and this heat is getting to us 
+With all 3 ac running it stays about 74 in the camper, which is fine. But hits up to 80 in the bedroom. What's yalls best tips and tricks to keeping the heat down without frying our ac units? 
+We have dehumidifiers, keep the window shades down and the windows are factory tinted (we will be putting darker tint on the windows soon). ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>data\images\hack_3513687305456890\img_1.jpg; data\images\hack_3513687305456890\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3513687305456890</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>40</v>
+      </c>
+      <c r="C14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4219763604824093/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Unfortunately, we purchased a 2021 Salem Cruise Lite 282QBXL in June and it has been nothing but trouble since. 
+On our first trip, the slide out wouldn’t retract all the way on its own (yes, I checked it prior to purchase and it seemed to work fine, but looking back, I think they had it jacked up on that side to help assist it and I just thought the driveway was pitched). It would get about a foot out and come to a stop. If I had it jacked up slightly and leaned into it, I ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_4219763604824093\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4219763604824093</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>40</v>
+      </c>
+      <c r="C15" t="n">
+        <v>85</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4219763604824093/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Unfortunately, we purchased a 2021 Salem Cruise Lite 282QBXL in June and it has been nothing but trouble since. 
+On our first trip, the slide out wouldn’t retract all the way on its own (yes, I checked it prior to purchase and it seemed to work fine, but looking back, I think they had it jacked up on that side to help assist it and I just thought the driveway was pitched). It would get about a foot out and come to a stop. If I had it jacked up slightly and leaned into it, I ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_4219763604824093\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>4219763604824093</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>21</v>
+      </c>
+      <c r="C16" t="n">
+        <v>75</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4242996285834158/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Question for the elite in this group. If I left the camper plugged in to shore power at home for weeks/months continuously in order to have 110V power. (Dehumidifier) Do y'all feel this will have a wear and tear effect on the converter that I could otherwise avoid by other means?</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>4242996285834158</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>21</v>
+      </c>
+      <c r="C17" t="n">
+        <v>75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4242996285834158/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Question for the elite in this group. If I left the camper plugged in to shore power at home for weeks/months continuously in order to have 110V power. (Dehumidifier) Do y'all feel this will have a wear and tear effect on the converter that I could otherwise avoid by other means?</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4242996285834158</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>19</v>
+      </c>
+      <c r="C18" t="n">
+        <v>55</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3581840501974903/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>So our refrigerator just went out in our RV. It’s a Norcold. We are full timers. We also had a mobile RV mechanic come check it. I’m wondering what experience others have had with putting in a regular residential fridge. We never boon dock so the propane option is worthless to us. Our mechanic told us we may have to take out the drawer underneath but we’re fine with that. Just wondering who else has put a regular residential fridge in... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3581840501974903</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>19</v>
+      </c>
+      <c r="C19" t="n">
+        <v>55</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3581840501974903/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>So our refrigerator just went out in our RV. It’s a Norcold. We are full timers. We also had a mobile RV mechanic come check it. I’m wondering what experience others have had with putting in a regular residential fridge. We never boon dock so the propane option is worthless to us. Our mechanic told us we may have to take out the drawer underneath but we’re fine with that. Just wondering who else has put a regular residential fridge in... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>3581840501974903</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="n">
+        <v>173</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4244102009056919/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>What is a good space heater to use in a camper?</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>4244102009056919</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="n">
+        <v>173</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4244102009056919/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>What is a good space heater to use in a camper?</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4244102009056919</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="n">
+        <v>39</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3622362671256019/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Thoughts….when parked at home  I keep my Class C plugged into shore power all the time.(months at a time) Is there any benefit to unplugging and letting the batteries work a little and then plugging in the charge them up?</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>3622362671256019</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" t="n">
+        <v>39</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3622362671256019/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Thoughts….when parked at home  I keep my Class C plugged into shore power all the time.(months at a time) Is there any benefit to unplugging and letting the batteries work a little and then plugging in the charge them up?</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>3622362671256019</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="n">
+        <v>26</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3628769393948680/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>3628769393948680</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" t="n">
+        <v>26</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3628769393948680/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>3628769393948680</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>32</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3218284608305336/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Does anyone have a great recommendation for a sofa with a pull out bed? There’s a lot of options for the kind that allows the sofa back to flatten, but it looks like we would have to pull it out from the wall every night. Probably the same for a futon. I would like it to be as simple as possible. It also needs to be comfortable. It will be used full time. 
+Thank you!</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>3218284608305336</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3218284608305336/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Does anyone have a great recommendation for a sofa with a pull out bed? There’s a lot of options for the kind that allows the sofa back to flatten, but it looks like we would have to pull it out from the wall every night. Probably the same for a futon. I would like it to be as simple as possible. It also needs to be comfortable. It will be used full time. 
+Thank you!</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3218284608305336</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>48</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>3359003754258580</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>48</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>3359003754258580</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>55</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3629156827243270/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Okay, y’all…we officially did a thing!
+My husband and I just bought our first camper — a 2022 Cherokee Grey Wolf Limited 27RR — and we are COMPLETE newbies to the camping world. We’ve always enjoyed getting away, but this is our first time actually owning a camper, so I’m about to learn A LOT.
+We also have a Can-Am Defender that we can haul in the toy hauler, although we’ll probably use it more for hunting trips than camping.... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>3629156827243270</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>32</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>data\images\hack_4147910648676056\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>4147910648676056</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>55</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3629156827243270/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Okay, y’all…we officially did a thing!
+My husband and I just bought our first camper — a 2022 Cherokee Grey Wolf Limited 27RR — and we are COMPLETE newbies to the camping world. We’ve always enjoyed getting away, but this is our first time actually owning a camper, so I’m about to learn A LOT.
+We also have a Can-Am Defender that we can haul in the toy hauler, although we’ll probably use it more for hunting trips than camping.... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>3629156827243270</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>32</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>data\images\hack_4147910648676056\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>4147910648676056</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>34</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>3128604820606649</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>36</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3617867058372247</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" t="n">
+        <v>34</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>3128604820606649</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>36</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>3617867058372247</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>43</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3631536470338639/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Need recommendation for a new mattress! Prefer medium firm!</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>3631536470338639</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>43</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3631536470338639/</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Need recommendation for a new mattress! Prefer medium firm!</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3631536470338639</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>177</v>
+      </c>
+      <c r="D40" t="n">
+        <v>278</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/2790989414393353/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>This collapsible pet pool from Aldi fits perfectly in the neo angle shower. Might be useful for those of you with pets or kiddos who would like a bath. They sell them on amazon too.
+Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>2790989414393353</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>177</v>
+      </c>
+      <c r="D41" t="n">
+        <v>278</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/2790989414393353/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>This collapsible pet pool from Aldi fits perfectly in the neo angle shower. Might be useful for those of you with pets or kiddos who would like a bath. They sell them on amazon too.
+Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2790989414393353</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>85</v>
+      </c>
+      <c r="D42" t="n">
+        <v>41</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3498835016916959/</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3498835016916959</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>85</v>
+      </c>
+      <c r="D43" t="n">
+        <v>41</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3498835016916959/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>3498835016916959</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>71</v>
+      </c>
+      <c r="D44" t="n">
+        <v>54</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3080238785468413/</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>It was so annoying I couldn’t put my tailgate all the way down! So flipped this and problem solved !</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>3080238785468413</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>71</v>
+      </c>
+      <c r="D45" t="n">
+        <v>54</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3080238785468413/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>It was so annoying I couldn’t put my tailgate all the way down! So flipped this and problem solved !</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3080238785468413</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/reports/viral_posts.xlsx
+++ b/data/reports/viral_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,80 +489,118 @@
           <t>image_urls</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>is_product</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>product_category</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>amazon_query</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>winner_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>521</v>
+      </c>
+      <c r="C2" t="n">
+        <v>81</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4124414001025721/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Our 19 year old daughter didn't exactly wanna squeeze into the bunkhouse 
+ so her Dad and I did this for her. We just bought this 2026 Catalina Legacy Edition 273dbh ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_4124414001025721\img_1.jpg; data\images\must_have_gadget_4124414001025721\img_2.jpg; data\images\must_have_gadget_4124414001025721\img_3.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4124414001025721</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/714611806_10215958763359663_6601841730117456563_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1386x2048&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=e1O3zMI2FBAQ7kNvwH0f9kz&amp;_nc_oc=Adrlw0O8ab8aboNq_-Issv4ZciryIkKZBDfmyzFxZiGWadT3Gk3TKsaWld3S8OPoobk&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI4ZelcCflvqEJ2kpSSxWFEzejtqTMDMQQyV93rqWUKtQ&amp;oe=6AB3BC85; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/714384150_10215958763759673_8245354785028741008_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx935x1272&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=FpOY9vQtJ6YQ7kNvwGRrp_C&amp;_nc_oc=AdqVcmZxnd_HmBnrMWMo1IQwxCZhT3KzI9F-kZeoGmuIlDtWr_BOud5c2P1J1ogRNTQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLJppTjdJa-7osH0NPYnAJCp__ERaaJzgRYx4xQGpdzUA&amp;oe=6AB39A9B; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715435401_10215958764119682_4239662220553189837_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x2048&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=Lgyxk1qwPP8Q7kNvwExOJLi&amp;_nc_oc=AdrFTRRleOoNTZXioS5hSn97k-U5pLE8wzdP2Th_-pYVRRRQHaSxcAxUNJWUmBCyl3Y&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKXWP-_umRYvMmKVNdu03tTuOXsQLCnkNnzHA-iQQCm2w&amp;oe=6AB3B4D0</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>492</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>69</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/2389439124523226/</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>17 weeks of hard work- but our total transformation is done! ...well mostly done 
 We are so happy!!</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>data\images\hack_2389439124523226\img_1.jpg; data\images\hack_2389439124523226\img_2.jpg; data\images\hack_2389439124523226\img_3.jpg; data\images\hack_2389439124523226\img_4.jpg; data\images\hack_2389439124523226\img_5.jpg</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>2389439124523226</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>492</v>
-      </c>
-      <c r="C3" t="n">
-        <v>69</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/2389439124523226/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>17 weeks of hard work- but our total transformation is done! ...well mostly done 
-We are so happy!!</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>data\images\hack_2389439124523226\img_1.jpg; data\images\hack_2389439124523226\img_2.jpg; data\images\hack_2389439124523226\img_3.jpg; data\images\hack_2389439124523226\img_4.jpg; data\images\hack_2389439124523226\img_5.jpg</t>
@@ -574,10 +612,8 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2389439124523226</t>
-        </is>
+      <c r="J3" t="n">
+        <v>2389439124523226</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
@@ -585,6 +621,22 @@
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
         </is>
       </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>rv hack</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -622,10 +674,8 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3308082032658926</t>
-        </is>
+      <c r="J4" t="n">
+        <v>3308082032658926</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
@@ -633,35 +683,39 @@
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>must have gadget</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>377</v>
+        <v>162</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3308082032658926/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4009327692534353/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Our camper didn’t come with a ladder to the upper bunks. My girls struggle to climb up to them to play. So I wanted a ladder but not too tall. I ended up getting a trampoline ladder. It cost only $25 and just hooked onto the bunk</t>
+          <t>What’s your “why did no one tell me I needed this?” item for camping?... عرض المزيد</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>data\images\hack_3308082032658926\img_1.jpg</t>
+          <t>data\images\must_have_gadget_4009327692534353\img_1.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -670,44 +724,66 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>3308082032658926</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4009327692534353</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
-        </is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/643396407_10238655093303438_2982570874296650007_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QvAD0_ZeHdEQ7kNvwHy778z&amp;_nc_oc=AdqBe3rZBJ3X2Tj7tMqgAfl7NMUdiQQd8sMoyfXjYeHH-8ewyBv_yNBoyhPsZucF3yA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIUChpHh0PDussfNot-ZthDMoiDU_kAzhX2nuuDxqd_Xg&amp;oe=6AB3C10F</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>amazon find</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C6" t="n">
-        <v>326</v>
+        <v>109</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3353573731443089/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4113730608760727/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Any ideas on how to not get your camper to shake? I have not been able to sleep at all because I literally feel the kids move in their sleep.  We bought the x jack to help but it’s still not working.  Any suggestions!</t>
+          <t>Update photo added to comments!
+I went with the vinyl to hide the ugly and add some whimsy and some blackout curtains to make sure it stays nice and dark
+Thank you all for the wonderful suggestions!
+Question!
+عرض المزيد</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>data\images\hack_3353573731443089\img_1.jpg</t>
+          <t>data\images\amazon_find_4113730608760727\img_1.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -716,92 +792,128 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>3353573731443089</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4113730608760727</t>
+        </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
-        </is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710710608_3365719276935810_913380809031877934_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1290x1728&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=W4Mx_7udmmcQ7kNvwFJ4xZI&amp;_nc_oc=AdqFT1td-gxh5OjykSM57gmwHH8rg2J4DkAgoVkCftj1D8ioDF6ymqGPV7zwA4SlLIs&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQJVruWyQvhPwbT7S7oAFjSG9T7OumAe5miDQecXxPLwqw&amp;oe=6AB3B1EB</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>rv amazon find</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>must have gadget</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>326</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3353573731443089/</t>
+          <t>https://www.facebook.com/177043908</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Any ideas on how to not get your camper to shake? I have not been able to sleep at all because I literally feel the kids move in their sleep.  We bought the x jack to help but it’s still not working.  Any suggestions!</t>
+          <t>I'm not sure which few asked for an update. Here it is. I hope this helps. 
+UPDATE: I attached a photo of my closet organizer since some wanted to see more of a closer view. What i forgot to mention earlier are the "can't do without" lightening. I put 3 in my closet due to it getting very dark in there with clothes on racks. So I put a light on each level of clothes. This came in handy all last week. 
+As for laundry bag thing on wall, after testing it out this last week... ... عرض المزيد</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>data\images\hack_3353573731443089\img_1.jpg</t>
+          <t>data\images\must_have_gadget_177043908\img_1.jpg; data\images\must_have_gadget_177043908\img_2.jpg; data\images\must_have_gadget_177043908\img_3.jpg; data\images\must_have_gadget_177043908\img_4.jpg; data\images\must_have_gadget_177043908\img_5.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RVhackcamp</t>
+          <t>Public Search</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3353573731443089</t>
+          <t>177043908</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
-        </is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655900116_26426801810294266_616338587343076791_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=jB-xL4WCwAgQ7kNvwFsIIDC&amp;_nc_oc=AdoGV6P4nAjOyR8A4bqzpg8FsSFsTzuA9J9oYzN3nvHnZSZOlC6sXJaEQPLvrs9zuXc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLUYw_U16e1OluoKTx7qceTxgRUASaIWKPWYSNAPF7z1w&amp;oe=6AB3AB8A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/656840747_26426801883627592_1775700405554872607_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=j8NFBjoOyBgQ7kNvwGMUo7s&amp;_nc_oc=AdqOeMpnaO7GTgDmhNWFl03ZZ_QL7ZHss7jWCq2a7ZYSMXuKGE1WUJ9CfjqRoFvo9eU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQJRDiTDfLxEoM8Xrvq6SX0XMQ3iNan62a_aWFxF6SNbTQ&amp;oe=6AB3A8C1; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657150247_26426801800294267_4229617446844769500_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5uBeSm0hyV4Q7kNvwH9eak5&amp;_nc_oc=AdqD-e9fhg29P5ptbb-bxoATLpJLzKa5ChpOU3XznPSRGg45TbRqnGiekZ-Fj2fFdn0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQKg6QyAcUm2tguTzAJn5IZvx9Qg5619GpKKp-wmYaZQRQ&amp;oe=6AB3A834; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654788918_26426801906960923_9152926241027148999_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4RIBSqLMeMwQ7kNvwHiyBp2&amp;_nc_oc=AdoFw7HCp0WiCNPFdtTg_qOn24YtaAUsamWcP_0v6RFoomJsna8Gnk8_8s_weRijukI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLX2ScQA5L21ZhRwZqfvML7zcU4HXflbHCENha7umNhbw&amp;oe=6AB3BD78; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657400660_26426801690294278_6323538386743307505_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=UVxsV1XnU1YQ7kNvwH4wdgb&amp;_nc_oc=AdoRtrvoNkiOrIL8az4oODToaK-5CuEH5v8d56ZqqHZ8_rABt700zdiT_V3Zsx3XWtI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQK1Agtjk-e11HuLDvO8Mo64I7XyMomEEkyGgv6D6jwABQ&amp;oe=6AB399F0</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>تنظيم وتخزين (Storage &amp; Organization)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>rv hanging shoe organizer</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3845725655561225/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3353573731443089/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
+          <t>Any ideas on how to not get your camper to shake? I have not been able to sleep at all because I literally feel the kids move in their sleep.  We bought the x jack to help but it’s still not working.  Any suggestions!</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
+          <t>data\images\hack_3353573731443089\img_1.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -810,46 +922,61 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>3845725655561225</t>
-        </is>
+      <c r="J8" t="n">
+        <v>3353573731443089</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
-        </is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>rv stabilizer x chock</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>must have gadget</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>97</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3845725655561225/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3339400259527103/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
+          <t>Posting at the risk of looking dumb 
+. We are newbies at camping. We are camping for our second time and we have hot water but it doesn't last long. We DIDNT have this switch on and the water was very hot but didn't even last one shower. Does this switch do something to make the hot water last longer? We are at a full hook up site. Coachmen Catalina legacy camper.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
+          <t>data\images\must_have_gadget_3339400259527103\img_1.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -858,133 +985,296 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>3845725655561225</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3339400259527103</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
-        </is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/504466196_30951392407793645_1083003521996665110_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PKBd6m8794QQ7kNvwHv6k2T&amp;_nc_oc=AdqXfd2GEhQ2tfaXL2IkQ5e03U05M1IagmAMktvw6im0SvIyX2X0BXBusblw6qbLA9Q&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI0GDL8YgVHTfZhhbmWGQfWuXOAXKGlyQLPLfy17BdcbA&amp;oe=6AB397B0</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>124</v>
+      </c>
+      <c r="C10" t="n">
+        <v>343</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3845725655561225/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3845725655561225</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>amazon find</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>104</v>
+      </c>
+      <c r="C11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/791791057</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>You guys were so helpful when I asked for advice so I thought I’d share a few of my “hacks” to maybe help someone else! ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_791791057\img_1.jpg; data\images\amazon_find_791791057\img_2.jpg; data\images\amazon_find_791791057\img_3.jpg; data\images\amazon_find_791791057\img_4.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Public Search</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>791791057</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/718204993_3377270389114032_3017451080494617445_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=qYfYw4OVFlQQ7kNvwFzTUw2&amp;_nc_oc=AdrTdokM1V_C9TzLfjq5_yhdW9z1pnNrXAPOqM7sMo9zBm1IgAoSMyik8zLi5QctYCQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQKN6mRZQV1JOvOk5cGH3-J9bLpZnNAF30D41_tiHhRwqA&amp;oe=6AB393CE; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/719160410_3377257819115289_4512916211874135718_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx960x720&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=kme4VsbYGiQQ7kNvwF0UTnh&amp;_nc_oc=AdpLFsFTOQlfY2GtWNtHZkgfNauVxu3L28i1m9bTX7UjZW46L_6uJXsumd63ry3hM_E&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIpFVodpDrLXaNrm03MWNxcRUQTUe0bD15QwfGTs15G_A&amp;oe=6AB39474; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715749899_3377270385780699_46444169963824531_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=m1B9Z9a3XTcQ7kNvwHbSueQ&amp;_nc_oc=AdqZvLfkUECCp-PzosWPpwH6aKcCTcnp5LCTlPaQnAapvNYk3h0vr0MwYZ74N6JJE60&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIIaHm-ZLLeWqyzE87P30_-cNCHO9sQVloN5bT3aFotpg&amp;oe=6AB395EC; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/720495745_3377270445780693_888169211609445957_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PEd1aWG90c4Q7kNvwFfUOQ4&amp;_nc_oc=AdrTRXfrx1pomRzcompzkQAMeyuhMDOb6GxUxdzedExILCEZNRNmCOswHKYdYi-vFpY&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQJdSmbYZUx1bo6s6BUqTCImTGV2rJasH5LeKQDXXFya1A&amp;oe=6AB3A127</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>rv amazon find</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B12" t="n">
         <v>80</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C12" t="n">
         <v>92</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3583318008493819/</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>It's level, but still wobbles when walking inside.
 Can you knowledgeable friends tell me what you think of our set up. We've heard that not lowering the stabilizers all the way helps with the wobble.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>data\images\hack_3583318008493819\img_1.jpg; data\images\hack_3583318008493819\img_2.jpg; data\images\hack_3583318008493819\img_3.jpg</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>3583318008493819</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/763072132_10240527915834058_262860686266165320_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tQPKb_7z3scQ7kNvwHI1W7g&amp;_nc_oc=AdryOCOHLUetXqxLh_YB0dln50lhK5trI90T_Fm1qocc_zcSjKjM7rFYwajXvgsjhTI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJ0GnPf57poAwnS1tveFqIifG41xCwgcTXoj7nwXsPD0g&amp;oe=6AB39330; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/764719882_10240527916554076_6179174592261675065_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGePznIup-IQ7kNvwF8n1gs&amp;_nc_oc=AdpGktVoydqk0AxdQDAOzbx_Pf2MDjo3DIQObD1Zjm6Y7VQBbann44VUTt2JZv16NT8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJvlQLTekeLpX0VeuXsY7AW8BTlFEb4ontl07T28WmncA&amp;oe=6AB39768; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/762276276_10240527918834133_6935526286052437077_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=LUYt4ZPtFlQQ7kNvwFtDGTf&amp;_nc_oc=Ados7w7e5WTUF89zeazhrONFUSOjfR3KkU-WEt4FzNzv3RCM9gJpPLl89FV5RIzy0P4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQIUbRAOYKraspj5sBL0vF-0I_3MUiK5eLiusqFF-B6VQQ&amp;oe=6AB3908B</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>rv stabilizer x chock</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>71</v>
+      </c>
+      <c r="C13" t="n">
+        <v>176</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/2519590198174784/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hi all my husband and I bought our first ever brand new 2021 hideout! With one slideout! We bought it in April of this year! We were loving it so much, it was my dream ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_2519590198174784\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2519590198174784</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/489965465_10161600930962880_4833098666534324521_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1504x2015&amp;ctp=p526x296&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=536f4a&amp;_nc_ohc=xMIVUG5htDkQ7kNvwG8ehE-&amp;_nc_oc=Adp4sJx_jBWQxqAezLmKNS9_5TDHX2yXRWxyb3DDrZ3-anVVRKHC96Jtv_1gNntBUhE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKdYBPNRTeYp1FOp6-rBTffCUwYr55-PcsfEHer1NRGrw&amp;oe=6AB3994F</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>80</v>
-      </c>
-      <c r="C11" t="n">
-        <v>92</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3583318008493819/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>It's level, but still wobbles when walking inside.
-Can you knowledgeable friends tell me what you think of our set up. We've heard that not lowering the stabilizers all the way helps with the wobble.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>data\images\hack_3583318008493819\img_1.jpg; data\images\hack_3583318008493819\img_2.jpg; data\images\hack_3583318008493819\img_3.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3583318008493819</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/763072132_10240527915834058_262860686266165320_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tQPKb_7z3scQ7kNvwHI1W7g&amp;_nc_oc=AdryOCOHLUetXqxLh_YB0dln50lhK5trI90T_Fm1qocc_zcSjKjM7rFYwajXvgsjhTI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJ0GnPf57poAwnS1tveFqIifG41xCwgcTXoj7nwXsPD0g&amp;oe=6AB39330; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/764719882_10240527916554076_6179174592261675065_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGePznIup-IQ7kNvwF8n1gs&amp;_nc_oc=AdpGktVoydqk0AxdQDAOzbx_Pf2MDjo3DIQObD1Zjm6Y7VQBbann44VUTt2JZv16NT8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJvlQLTekeLpX0VeuXsY7AW8BTlFEb4ontl07T28WmncA&amp;oe=6AB39768; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/762276276_10240527918834133_6935526286052437077_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=LUYt4ZPtFlQQ7kNvwFtDGTf&amp;_nc_oc=Ados7w7e5WTUF89zeazhrONFUSOjfR3KkU-WEt4FzNzv3RCM9gJpPLl89FV5RIzy0P4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQIUbRAOYKraspj5sBL0vF-0I_3MUiK5eLiusqFF-B6VQQ&amp;oe=6AB3908B</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+      <c r="B14" t="n">
         <v>54</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C14" t="n">
         <v>69</v>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3513687305456890/</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Hello everybody! 
 New, full time rv living here! 
@@ -993,201 +1283,129 @@
 We have dehumidifiers, keep the window shades down and the windows are factory tinted (we will be putting darker tint on the windows soon). ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>data\images\hack_3513687305456890\img_1.jpg; data\images\hack_3513687305456890\img_2.jpg</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3513687305456890</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="J14" t="n">
+        <v>3513687305456890</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>54</v>
-      </c>
-      <c r="C13" t="n">
-        <v>69</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3513687305456890/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Hello everybody! 
-New, full time rv living here! 
-We live in Texas and this heat is getting to us 
-With all 3 ac running it stays about 74 in the camper, which is fine. But hits up to 80 in the bedroom. What's yalls best tips and tricks to keeping the heat down without frying our ac units? 
-We have dehumidifiers, keep the window shades down and the windows are factory tinted (we will be putting darker tint on the windows soon). ... عرض المزيد</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>data\images\hack_3513687305456890\img_1.jpg; data\images\hack_3513687305456890\img_2.jpg</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>3513687305456890</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>amazon find</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>46</v>
+      </c>
+      <c r="C15" t="n">
+        <v>47</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/2956335967833536/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>We are getting ready to PCS soon and will be staying in our camper for about 6 weeks. I have 3 kids (7,4,&amp;2) 
+I’m struggling to find a good “baby proof” way to keep the doors closed. 
+The last time we went camping the 2 year old opened the door in the middle of the night. 
+Any suggestions on good locks? ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_2956335967833536\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2956335967833536</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/486263063_3431305033666747_2774947844339664550_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_V3lAOuS71gQ7kNvwG1HA6t&amp;_nc_oc=Ado0M-qFkVhQnVlLURz25aP5SNH_jAdpe4Dmc4HtVTUByPMy0vPdcFtq1ganZeRHiEc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQK8ZOwXZcwYIiJ5OsCjs7fTQm9bTUEleRwYHx_4DZJBiw&amp;oe=6AB39B39</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>rv amazon find</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B16" t="n">
         <v>40</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C16" t="n">
         <v>85</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/4219763604824093/</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Unfortunately, we purchased a 2021 Salem Cruise Lite 282QBXL in June and it has been nothing but trouble since. 
 On our first trip, the slide out wouldn’t retract all the way on its own (yes, I checked it prior to purchase and it seemed to work fine, but looking back, I think they had it jacked up on that side to help assist it and I just thought the driveway was pitched). It would get about a foot out and come to a stop. If I had it jacked up slightly and leaned into it, I ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>data\images\recommendation_4219763604824093\img_1.jpg</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>4219763604824093</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>40</v>
-      </c>
-      <c r="C15" t="n">
-        <v>85</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4219763604824093/</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Unfortunately, we purchased a 2021 Salem Cruise Lite 282QBXL in June and it has been nothing but trouble since. 
-On our first trip, the slide out wouldn’t retract all the way on its own (yes, I checked it prior to purchase and it seemed to work fine, but looking back, I think they had it jacked up on that side to help assist it and I just thought the driveway was pitched). It would get about a foot out and come to a stop. If I had it jacked up slightly and leaned into it, I ... عرض المزيد</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>data\images\recommendation_4219763604824093\img_1.jpg</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>4219763604824093</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>21</v>
-      </c>
-      <c r="C16" t="n">
-        <v>75</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4242996285834158/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Question for the elite in this group. If I left the camper plugged in to shore power at home for weeks/months continuously in order to have 110V power. (Dehumidifier) Do y'all feel this will have a wear and tear effect on the converter that I could otherwise avoid by other means?</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
@@ -1195,37 +1413,49 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4242996285834158</v>
+        <v>4219763604824093</v>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>amazon find</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4242996285834158/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4228244110642709/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Question for the elite in this group. If I left the camper plugged in to shore power at home for weeks/months continuously in order to have 110V power. (Dehumidifier) Do y'all feel this will have a wear and tear effect on the converter that I could otherwise avoid by other means?</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>My stinky slinky won’t fit in the bumper tubing. Any ideas?</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_4228244110642709\img_1.jpg</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
@@ -1234,51 +1464,95 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4242996285834158</t>
+          <t>4228244110642709</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/789447152_10244813111573647_47739271540443468_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx720x1280&amp;ctp=p526x296&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9RQ21jppgcUQ7kNvwHOPHq-&amp;_nc_oc=AdpS_m5-K5_RU2sUwoQJWJrY-sl4KHrcU30zbIzSrUQ3R25NJhL2uHJx88ZWQYW0umU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKmJVCGhzzaIOrLJSB17QoEwCChxJioCHSDOxuyqiFvMA&amp;oe=6AB3A606</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>تنظيم وتخزين (Storage &amp; Organization)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>rv amazon find</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>must have gadget</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3581840501974903/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3605957036204756/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>So our refrigerator just went out in our RV. It’s a Norcold. We are full timers. We also had a mobile RV mechanic come check it. I’m wondering what experience others have had with putting in a regular residential fridge. We never boon dock so the propane option is worthless to us. Our mechanic told us we may have to take out the drawer underneath but we’re fine with that. Just wondering who else has put a regular residential fridge in... عرض المزيد</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Soo I want to paint the walls in my camper and I was wondering is there a certain paint or way to go about doing this? Below is what my walls look like in my camper.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_3605957036204756\img_1.jpg</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>roadtreking</t>
+          <t>RVhackcamp</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3581840501974903</t>
+          <t>3605957036204756</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/514417036_24232386396387276_8898425086872934580_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=0WuEyVKJSqkQ7kNvwGxzTrJ&amp;_nc_oc=AdpwYEulmgEEsjJgMkkuOg0h0LPQX5Bi_s7roUkZ1JKXJsLZhWL2MrHLy_UyPk1-mPA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKl3JPpvV7FsczmsCXiMGk3JcjuvjpM0ztQZBAozZpITg&amp;oe=6AB3CB59</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1287,36 +1561,48 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3581840501974903/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4242996285834158/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>So our refrigerator just went out in our RV. It’s a Norcold. We are full timers. We also had a mobile RV mechanic come check it. I’m wondering what experience others have had with putting in a regular residential fridge. We never boon dock so the propane option is worthless to us. Our mechanic told us we may have to take out the drawer underneath but we’re fine with that. Just wondering who else has put a regular residential fridge in... عرض المزيد</t>
+          <t>Question for the elite in this group. If I left the camper plugged in to shore power at home for weeks/months continuously in order to have 110V power. (Dehumidifier) Do y'all feel this will have a wear and tear effect on the converter that I could otherwise avoid by other means?</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>roadtreking</t>
+          <t>RVhackcamp</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3581840501974903</v>
+        <v>4242996285834158</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1325,36 +1611,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4244102009056919/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3581840501974903/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>What is a good space heater to use in a camper?</t>
+          <t>So our refrigerator just went out in our RV. It’s a Norcold. We are full timers. We also had a mobile RV mechanic come check it. I’m wondering what experience others have had with putting in a regular residential fridge. We never boon dock so the propane option is worthless to us. Our mechanic told us we may have to take out the drawer underneath but we’re fine with that. Just wondering who else has put a regular residential fridge in... عرض المزيد</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RVhackcamp</t>
+          <t>roadtreking</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4244102009056919</v>
+        <v>3581840501974903</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1388,13 +1678,23 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>4244102009056919</t>
-        </is>
+      <c r="J21" t="n">
+        <v>4244102009056919</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1428,40 +1728,46 @@
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>3622362671256019</t>
-        </is>
+      <c r="J22" t="n">
+        <v>3622362671256019</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3622362671256019/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3628769393948680/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thoughts….when parked at home  I keep my Class C plugged into shore power all the time.(months at a time) Is there any benefit to unplugging and letting the batteries work a little and then plugging in the charge them up?</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
@@ -1469,10 +1775,26 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3622362671256019</v>
+        <v>3628769393948680</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>غير مؤكد (نقاش عام)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1481,43 +1803,48 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3628769393948680/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3218284608305336/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
-        </is>
-      </c>
+          <t>Does anyone have a great recommendation for a sofa with a pull out bed? There’s a lot of options for the kind that allows the sofa back to flatten, but it looks like we would have to pull it out from the wall every night. Probably the same for a futon. I would like it to be as simple as possible. It also needs to be comfortable. It will be used full time. 
+Thank you!</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>roadtreking</t>
+          <t>RVhackcamp</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3628769393948680</v>
+        <v>3218284608305336</v>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
-        </is>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1527,45 +1854,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3628769393948680/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3629156827243270/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
-        </is>
-      </c>
+          <t>Okay, y’all…we officially did a thing!
+My husband and I just bought our first camper — a 2022 Cherokee Grey Wolf Limited 27RR — and we are COMPLETE newbies to the camping world. We’ve always enjoyed getting away, but this is our first time actually owning a camper, so I’m about to learn A LOT.
+We also have a Can-Am Defender that we can haul in the toy hauler, although we’ll probably use it more for hunting trips than camping.... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>3628769393948680</t>
-        </is>
+      <c r="J25" t="n">
+        <v>3629156827243270</v>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
-        </is>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1575,46 +1906,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3218284608305336/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Does anyone have a great recommendation for a sofa with a pull out bed? There’s a lot of options for the kind that allows the sofa back to flatten, but it looks like we would have to pull it out from the wall every night. Probably the same for a futon. I would like it to be as simple as possible. It also needs to be comfortable. It will be used full time. 
-Thank you!</t>
+          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>RVhackcamp</t>
+          <t>roadtreking</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3218284608305336</v>
+        <v>3359003754258580</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>amazon find</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
         <v>32</v>
@@ -1624,16 +1958,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3218284608305336/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Does anyone have a great recommendation for a sofa with a pull out bed? There’s a lot of options for the kind that allows the sofa back to flatten, but it looks like we would have to pull it out from the wall every night. Probably the same for a futon. I would like it to be as simple as possible. It also needs to be comfortable. It will be used full time. 
-Thank you!</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_4147910648676056\img_1.jpg</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
@@ -1642,51 +1979,93 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3218284608305336</t>
+          <t>4147910648676056</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKuI7NhSiWUW3pweIYcuSccGm2fBiXhQmnukqpjQKDiRg&amp;oe=6AB3C7D6</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>rv 12v portable bunk fan</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>data\images\hack_4147910648676056\img_1.jpg</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>3359003754258580</t>
-        </is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>4147910648676056</v>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>rv 12v portable bunk fan</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1695,36 +2074,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
+          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>roadtreking</t>
+          <t>RVhackcamp</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>3359003754258580</v>
+        <v>3128604820606649</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1733,24 +2116,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3629156827243270/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Okay, y’all…we officially did a thing!
-My husband and I just bought our first camper — a 2022 Cherokee Grey Wolf Limited 27RR — and we are COMPLETE newbies to the camping world. We’ve always enjoyed getting away, but this is our first time actually owning a camper, so I’m about to learn A LOT.
-We also have a Can-Am Defender that we can haul in the toy hauler, although we’ll probably use it more for hunting trips than camping.... عرض المزيد</t>
+          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1761,98 +2142,135 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3629156827243270</v>
+        <v>3617867058372247</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3631536470338639/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>data\images\hack_4147910648676056\img_1.jpg</t>
-        </is>
-      </c>
+          <t>Need recommendation for a new mattress! Prefer medium firm!</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>RVhackcamp</t>
+          <t>roadtreking</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4147910648676056</v>
+        <v>3631536470338639</v>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
-        </is>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3629156827243270/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/2790989414393353/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Okay, y’all…we officially did a thing!
-My husband and I just bought our first camper — a 2022 Cherokee Grey Wolf Limited 27RR — and we are COMPLETE newbies to the camping world. We’ve always enjoyed getting away, but this is our first time actually owning a camper, so I’m about to learn A LOT.
-We also have a Can-Am Defender that we can haul in the toy hauler, although we’ll probably use it more for hunting trips than camping.... عرض المزيد</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>This collapsible pet pool from Aldi fits perfectly in the neo angle shower. Might be useful for those of you with pets or kiddos who would like a bath. They sell them on amazon too.
+Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>3629156827243270</t>
-        </is>
+      <c r="J32" t="n">
+        <v>2790989414393353</v>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>rv collapsible pet pool</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1861,27 +2279,27 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3498835016916959/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+          <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>data\images\hack_4147910648676056\img_1.jpg</t>
+          <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1890,534 +2308,80 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>4147910648676056</t>
-        </is>
+      <c r="J33" t="n">
+        <v>3498835016916959</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
-        </is>
-      </c>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3080238785468413/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>It was so annoying I couldn’t put my tailgate all the way down! So flipped this and problem solved !</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>3128604820606649</t>
-        </is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3080238785468413</v>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>7</v>
-      </c>
-      <c r="C35" t="n">
-        <v>36</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>3617867058372247</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>7</v>
-      </c>
-      <c r="C36" t="n">
-        <v>34</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>3128604820606649</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>7</v>
-      </c>
-      <c r="C37" t="n">
-        <v>36</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>3617867058372247</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" t="n">
-        <v>43</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3631536470338639/</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Need recommendation for a new mattress! Prefer medium firm!</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>3631536470338639</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C39" t="n">
-        <v>43</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3631536470338639/</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Need recommendation for a new mattress! Prefer medium firm!</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>3631536470338639</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" t="n">
-        <v>177</v>
-      </c>
-      <c r="D40" t="n">
-        <v>278</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/2790989414393353/</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>This collapsible pet pool from Aldi fits perfectly in the neo angle shower. Might be useful for those of you with pets or kiddos who would like a bath. They sell them on amazon too.
-Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>2790989414393353</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3</v>
-      </c>
-      <c r="C41" t="n">
-        <v>177</v>
-      </c>
-      <c r="D41" t="n">
-        <v>278</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/2790989414393353/</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>This collapsible pet pool from Aldi fits perfectly in the neo angle shower. Might be useful for those of you with pets or kiddos who would like a bath. They sell them on amazon too.
-Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2790989414393353</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" t="n">
-        <v>85</v>
-      </c>
-      <c r="D42" t="n">
-        <v>41</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3498835016916959/</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>3498835016916959</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" t="n">
-        <v>85</v>
-      </c>
-      <c r="D43" t="n">
-        <v>41</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3498835016916959/</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>3498835016916959</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="n">
-        <v>71</v>
-      </c>
-      <c r="D44" t="n">
-        <v>54</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3080238785468413/</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>It was so annoying I couldn’t put my tailgate all the way down! So flipped this and problem solved !</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>3080238785468413</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
-        <v>71</v>
-      </c>
-      <c r="D45" t="n">
-        <v>54</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3080238785468413/</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>It was so annoying I couldn’t put my tailgate all the way down! So flipped this and problem solved !</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>3080238785468413</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
-        </is>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>tailgate jack clearance flip</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/reports/viral_posts.xlsx
+++ b/data/reports/viral_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,10 +547,8 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4124414001025721</t>
-        </is>
+      <c r="J2" t="n">
+        <v>4124414001025721</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
@@ -578,94 +576,97 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>521</v>
+      </c>
+      <c r="C3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4124414001025721/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Our 19 year old daughter didn't exactly wanna squeeze into the bunkhouse 
+ so her Dad and I did this for her. We just bought this 2026 Catalina Legacy Edition 273dbh ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_4124414001025721\img_1.jpg; data\images\must_have_gadget_4124414001025721\img_2.jpg; data\images\must_have_gadget_4124414001025721\img_3.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4124414001025721</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/714611806_10215958763359663_6601841730117456563_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1386x2048&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=e1O3zMI2FBAQ7kNvwH0f9kz&amp;_nc_oc=Adrlw0O8ab8aboNq_-Issv4ZciryIkKZBDfmyzFxZiGWadT3Gk3TKsaWld3S8OPoobk&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI4ZelcCflvqEJ2kpSSxWFEzejtqTMDMQQyV93rqWUKtQ&amp;oe=6AB3BC85; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/714384150_10215958763759673_8245354785028741008_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx935x1272&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=FpOY9vQtJ6YQ7kNvwGRrp_C&amp;_nc_oc=AdqVcmZxnd_HmBnrMWMo1IQwxCZhT3KzI9F-kZeoGmuIlDtWr_BOud5c2P1J1ogRNTQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLJppTjdJa-7osH0NPYnAJCp__ERaaJzgRYx4xQGpdzUA&amp;oe=6AB39A9B; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715435401_10215958764119682_4239662220553189837_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x2048&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=Lgyxk1qwPP8Q7kNvwExOJLi&amp;_nc_oc=AdrFTRRleOoNTZXioS5hSn97k-U5pLE8wzdP2Th_-pYVRRRQHaSxcAxUNJWUmBCyl3Y&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKXWP-_umRYvMmKVNdu03tTuOXsQLCnkNnzHA-iQQCm2w&amp;oe=6AB3B4D0</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>492</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>69</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/2389439124523226/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>17 weeks of hard work- but our total transformation is done! ...well mostly done 
 We are so happy!!</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>data\images\hack_2389439124523226\img_1.jpg; data\images\hack_2389439124523226\img_2.jpg; data\images\hack_2389439124523226\img_3.jpg; data\images\hack_2389439124523226\img_4.jpg; data\images\hack_2389439124523226\img_5.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2389439124523226</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>rv hack</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>377</v>
-      </c>
-      <c r="C4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3308082032658926/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Our camper didn’t come with a ladder to the upper bunks. My girls struggle to climb up to them to play. So I wanted a ladder but not too tall. I ended up getting a trampoline ladder. It cost only $25 and just hooked onto the bunk</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>data\images\hack_3308082032658926\img_1.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -674,48 +675,59 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>3308082032658926</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2389439124523226</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>must have gadget</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>162</v>
+        <v>492</v>
       </c>
       <c r="C5" t="n">
-        <v>353</v>
+        <v>69</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4009327692534353/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/2389439124523226/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>What’s your “why did no one tell me I needed this?” item for camping?... عرض المزيد</t>
+          <t>17 weeks of hard work- but our total transformation is done! ...well mostly done 
+We are so happy!!</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>data\images\must_have_gadget_4009327692534353\img_1.jpg</t>
+          <t>data\images\hack_2389439124523226\img_1.jpg; data\images\hack_2389439124523226\img_2.jpg; data\images\hack_2389439124523226\img_3.jpg; data\images\hack_2389439124523226\img_4.jpg; data\images\hack_2389439124523226\img_5.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -724,15 +736,13 @@
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>4009327692534353</t>
-        </is>
+      <c r="J5" t="n">
+        <v>2389439124523226</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/643396407_10238655093303438_2982570874296650007_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QvAD0_ZeHdEQ7kNvwHy778z&amp;_nc_oc=AdqBe3rZBJ3X2Tj7tMqgAfl7NMUdiQQd8sMoyfXjYeHH-8ewyBv_yNBoyhPsZucF3yA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIUChpHh0PDussfNot-ZthDMoiDU_kAzhX2nuuDxqd_Xg&amp;oe=6AB3C10F</t>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -740,39 +750,279 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+          <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>rv must have gadget</t>
+          <t>rv hack</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>377</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3308082032658926/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Our camper didn’t come with a ladder to the upper bunks. My girls struggle to climb up to them to play. So I wanted a ladder but not too tall. I ended up getting a trampoline ladder. It cost only $25 and just hooked onto the bunk</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>data\images\hack_3308082032658926\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3308082032658926</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>377</v>
+      </c>
+      <c r="C7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3308082032658926/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Our camper didn’t come with a ladder to the upper bunks. My girls struggle to climb up to them to play. So I wanted a ladder but not too tall. I ended up getting a trampoline ladder. It cost only $25 and just hooked onto the bunk</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>data\images\hack_3308082032658926\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3308082032658926</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>تنظيم وتخزين جاهز (Storage &amp; Organization)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>bunk bed trampoline ladder</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>162</v>
+      </c>
+      <c r="C8" t="n">
+        <v>353</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4009327692534353/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>What’s your “why did no one tell me I needed this?” item for camping?... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_4009327692534353\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4009327692534353</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/643396407_10238655093303438_2982570874296650007_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QvAD0_ZeHdEQ7kNvwHy778z&amp;_nc_oc=AdqBe3rZBJ3X2Tj7tMqgAfl7NMUdiQQd8sMoyfXjYeHH-8ewyBv_yNBoyhPsZucF3yA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIUChpHh0PDussfNot-ZthDMoiDU_kAzhX2nuuDxqd_Xg&amp;oe=6AB3C10F</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>162</v>
+      </c>
+      <c r="C9" t="n">
+        <v>353</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4009327692534353/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>What’s your “why did no one tell me I needed this?” item for camping?... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_4009327692534353\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>4009327692534353</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/643396407_10238655093303438_2982570874296650007_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QvAD0_ZeHdEQ7kNvwHy778z&amp;_nc_oc=AdqBe3rZBJ3X2Tj7tMqgAfl7NMUdiQQd8sMoyfXjYeHH-8ewyBv_yNBoyhPsZucF3yA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIUChpHh0PDussfNot-ZthDMoiDU_kAzhX2nuuDxqd_Xg&amp;oe=6AB3C10F</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>amazon find</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" t="n">
         <v>153</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C10" t="n">
         <v>109</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/4113730608760727/</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Update photo added to comments!
 I went with the vinyl to hide the ugly and add some whimsy and some blackout curtains to make sure it stays nice and dark
@@ -781,500 +1031,1002 @@
 عرض المزيد</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>data\images\amazon_find_4113730608760727\img_1.jpg</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J10" t="n">
+        <v>4113730608760727</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710710608_3365719276935810_913380809031877934_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1290x1728&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=W4Mx_7udmmcQ7kNvwFJ4xZI&amp;_nc_oc=AdqFT1td-gxh5OjykSM57gmwHH8rg2J4DkAgoVkCftj1D8ioDF6ymqGPV7zwA4SlLIs&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQJVruWyQvhPwbT7S7oAFjSG9T7OumAe5miDQecXxPLwqw&amp;oe=6AB3B1EB</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>rv amazon find</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>amazon find</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>153</v>
+      </c>
+      <c r="C11" t="n">
+        <v>109</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4113730608760727/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Update photo added to comments!
+I went with the vinyl to hide the ugly and add some whimsy and some blackout curtains to make sure it stays nice and dark
+Thank you all for the wonderful suggestions!
+Question!
+عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_4113730608760727\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>4113730608760727</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710710608_3365719276935810_913380809031877934_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1290x1728&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=W4Mx_7udmmcQ7kNvwFJ4xZI&amp;_nc_oc=AdqFT1td-gxh5OjykSM57gmwHH8rg2J4DkAgoVkCftj1D8ioDF6ymqGPV7zwA4SlLIs&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQJVruWyQvhPwbT7S7oAFjSG9T7OumAe5miDQecXxPLwqw&amp;oe=6AB3B1EB</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="P11" t="n">
         <v>73</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>must have gadget</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B12" t="n">
         <v>135</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C12" t="n">
         <v>25</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://www.facebook.com/177043908</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>I'm not sure which few asked for an update. Here it is. I hope this helps. 
 UPDATE: I attached a photo of my closet organizer since some wanted to see more of a closer view. What i forgot to mention earlier are the "can't do without" lightening. I put 3 in my closet due to it getting very dark in there with clothes on racks. So I put a light on each level of clothes. This came in handy all last week. 
 As for laundry bag thing on wall, after testing it out this last week... ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_177043908\img_1.jpg; data\images\must_have_gadget_177043908\img_2.jpg; data\images\must_have_gadget_177043908\img_3.jpg; data\images\must_have_gadget_177043908\img_4.jpg; data\images\must_have_gadget_177043908\img_5.jpg</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Public Search</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>177043908</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655900116_26426801810294266_616338587343076791_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=jB-xL4WCwAgQ7kNvwFsIIDC&amp;_nc_oc=AdoGV6P4nAjOyR8A4bqzpg8FsSFsTzuA9J9oYzN3nvHnZSZOlC6sXJaEQPLvrs9zuXc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLUYw_U16e1OluoKTx7qceTxgRUASaIWKPWYSNAPF7z1w&amp;oe=6AB3AB8A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/656840747_26426801883627592_1775700405554872607_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=j8NFBjoOyBgQ7kNvwGMUo7s&amp;_nc_oc=AdqOeMpnaO7GTgDmhNWFl03ZZ_QL7ZHss7jWCq2a7ZYSMXuKGE1WUJ9CfjqRoFvo9eU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQJRDiTDfLxEoM8Xrvq6SX0XMQ3iNan62a_aWFxF6SNbTQ&amp;oe=6AB3A8C1; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657150247_26426801800294267_4229617446844769500_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5uBeSm0hyV4Q7kNvwH9eak5&amp;_nc_oc=AdqD-e9fhg29P5ptbb-bxoATLpJLzKa5ChpOU3XznPSRGg45TbRqnGiekZ-Fj2fFdn0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQKg6QyAcUm2tguTzAJn5IZvx9Qg5619GpKKp-wmYaZQRQ&amp;oe=6AB3A834; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654788918_26426801906960923_9152926241027148999_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4RIBSqLMeMwQ7kNvwHiyBp2&amp;_nc_oc=AdoFw7HCp0WiCNPFdtTg_qOn24YtaAUsamWcP_0v6RFoomJsna8Gnk8_8s_weRijukI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLX2ScQA5L21ZhRwZqfvML7zcU4HXflbHCENha7umNhbw&amp;oe=6AB3BD78; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657400660_26426801690294278_6323538386743307505_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=UVxsV1XnU1YQ7kNvwH4wdgb&amp;_nc_oc=AdoRtrvoNkiOrIL8az4oODToaK-5CuEH5v8d56ZqqHZ8_rABt700zdiT_V3Zsx3XWtI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQK1Agtjk-e11HuLDvO8Mo64I7XyMomEEkyGgv6D6jwABQ&amp;oe=6AB399F0</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>تنظيم وتخزين جاهز (Storage &amp; Organization)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>rv hanging shoe organizer</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>135</v>
+      </c>
+      <c r="C13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/177043908</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>I'm not sure which few asked for an update. Here it is. I hope this helps. 
+UPDATE: I attached a photo of my closet organizer since some wanted to see more of a closer view. What i forgot to mention earlier are the "can't do without" lightening. I put 3 in my closet due to it getting very dark in there with clothes on racks. So I put a light on each level of clothes. This came in handy all last week. 
+As for laundry bag thing on wall, after testing it out this last week... ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_177043908\img_1.jpg; data\images\must_have_gadget_177043908\img_2.jpg; data\images\must_have_gadget_177043908\img_3.jpg; data\images\must_have_gadget_177043908\img_4.jpg; data\images\must_have_gadget_177043908\img_5.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Public Search</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>177043908</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655900116_26426801810294266_616338587343076791_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=jB-xL4WCwAgQ7kNvwFsIIDC&amp;_nc_oc=AdoGV6P4nAjOyR8A4bqzpg8FsSFsTzuA9J9oYzN3nvHnZSZOlC6sXJaEQPLvrs9zuXc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLUYw_U16e1OluoKTx7qceTxgRUASaIWKPWYSNAPF7z1w&amp;oe=6AB3AB8A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/656840747_26426801883627592_1775700405554872607_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=j8NFBjoOyBgQ7kNvwGMUo7s&amp;_nc_oc=AdqOeMpnaO7GTgDmhNWFl03ZZ_QL7ZHss7jWCq2a7ZYSMXuKGE1WUJ9CfjqRoFvo9eU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQJRDiTDfLxEoM8Xrvq6SX0XMQ3iNan62a_aWFxF6SNbTQ&amp;oe=6AB3A8C1; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657150247_26426801800294267_4229617446844769500_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5uBeSm0hyV4Q7kNvwH9eak5&amp;_nc_oc=AdqD-e9fhg29P5ptbb-bxoATLpJLzKa5ChpOU3XznPSRGg45TbRqnGiekZ-Fj2fFdn0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQKg6QyAcUm2tguTzAJn5IZvx9Qg5619GpKKp-wmYaZQRQ&amp;oe=6AB3A834; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654788918_26426801906960923_9152926241027148999_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4RIBSqLMeMwQ7kNvwHiyBp2&amp;_nc_oc=AdoFw7HCp0WiCNPFdtTg_qOn24YtaAUsamWcP_0v6RFoomJsna8Gnk8_8s_weRijukI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLX2ScQA5L21ZhRwZqfvML7zcU4HXflbHCENha7umNhbw&amp;oe=6AB3BD78; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657400660_26426801690294278_6323538386743307505_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=UVxsV1XnU1YQ7kNvwH4wdgb&amp;_nc_oc=AdoRtrvoNkiOrIL8az4oODToaK-5CuEH5v8d56ZqqHZ8_rABt700zdiT_V3Zsx3XWtI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQK1Agtjk-e11HuLDvO8Mo64I7XyMomEEkyGgv6D6jwABQ&amp;oe=6AB399F0</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>تنظيم وتخزين (Storage &amp; Organization)</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>rv hanging shoe organizer</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="P13" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B14" t="n">
         <v>127</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C14" t="n">
         <v>326</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D14" t="n">
         <v>11</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/3353573731443089/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Any ideas on how to not get your camper to shake? I have not been able to sleep at all because I literally feel the kids move in their sleep.  We bought the x jack to help but it’s still not working.  Any suggestions!</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>data\images\hack_3353573731443089\img_1.jpg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J14" t="n">
         <v>3353573731443089</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>rv stabilizer x chock</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="P14" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>127</v>
+      </c>
+      <c r="C15" t="n">
+        <v>326</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3353573731443089/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Any ideas on how to not get your camper to shake? I have not been able to sleep at all because I literally feel the kids move in their sleep.  We bought the x jack to help but it’s still not working.  Any suggestions!</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>data\images\hack_3353573731443089\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3353573731443089</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>rv stabilizer x chock</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>must have gadget</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B16" t="n">
         <v>126</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C16" t="n">
         <v>97</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/3339400259527103/</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Posting at the risk of looking dumb 
 . We are newbies at camping. We are camping for our second time and we have hot water but it doesn't last long. We DIDNT have this switch on and the water was very hot but didn't even last one shower. Does this switch do something to make the hot water last longer? We are at a full hook up site. Coachmen Catalina legacy camper.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_3339400259527103\img_1.jpg</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>3339400259527103</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/504466196_30951392407793645_1083003521996665110_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PKBd6m8794QQ7kNvwHv6k2T&amp;_nc_oc=AdqXfd2GEhQ2tfaXL2IkQ5e03U05M1IagmAMktvw6im0SvIyX2X0BXBusblw6qbLA9Q&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI0GDL8YgVHTfZhhbmWGQfWuXOAXKGlyQLPLfy17BdcbA&amp;oe=6AB397B0</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>rv must have gadget</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>126</v>
+      </c>
+      <c r="C17" t="n">
+        <v>97</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3339400259527103/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Posting at the risk of looking dumb 
+. We are newbies at camping. We are camping for our second time and we have hot water but it doesn't last long. We DIDNT have this switch on and the water was very hot but didn't even last one shower. Does this switch do something to make the hot water last longer? We are at a full hook up site. Coachmen Catalina legacy camper.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_3339400259527103\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>3339400259527103</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/504466196_30951392407793645_1083003521996665110_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PKBd6m8794QQ7kNvwHv6k2T&amp;_nc_oc=AdqXfd2GEhQ2tfaXL2IkQ5e03U05M1IagmAMktvw6im0SvIyX2X0BXBusblw6qbLA9Q&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI0GDL8YgVHTfZhhbmWGQfWuXOAXKGlyQLPLfy17BdcbA&amp;oe=6AB397B0</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="P17" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B18" t="n">
         <v>124</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C18" t="n">
         <v>343</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D18" t="n">
         <v>11</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/3845725655561225/</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J18" t="n">
         <v>3845725655561225</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>124</v>
+      </c>
+      <c r="C19" t="n">
+        <v>343</v>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3845725655561225/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3845725655561225</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>amazon find</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B20" t="n">
         <v>104</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C20" t="n">
         <v>22</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://www.facebook.com/791791057</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>You guys were so helpful when I asked for advice so I thought I’d share a few of my “hacks” to maybe help someone else! ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>data\images\amazon_find_791791057\img_1.jpg; data\images\amazon_find_791791057\img_2.jpg; data\images\amazon_find_791791057\img_3.jpg; data\images\amazon_find_791791057\img_4.jpg</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Public Search</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>791791057</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/718204993_3377270389114032_3017451080494617445_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=qYfYw4OVFlQQ7kNvwFzTUw2&amp;_nc_oc=AdrTdokM1V_C9TzLfjq5_yhdW9z1pnNrXAPOqM7sMo9zBm1IgAoSMyik8zLi5QctYCQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQKN6mRZQV1JOvOk5cGH3-J9bLpZnNAF30D41_tiHhRwqA&amp;oe=6AB393CE; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/719160410_3377257819115289_4512916211874135718_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx960x720&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=kme4VsbYGiQQ7kNvwF0UTnh&amp;_nc_oc=AdpLFsFTOQlfY2GtWNtHZkgfNauVxu3L28i1m9bTX7UjZW46L_6uJXsumd63ry3hM_E&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIpFVodpDrLXaNrm03MWNxcRUQTUe0bD15QwfGTs15G_A&amp;oe=6AB39474; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715749899_3377270385780699_46444169963824531_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=m1B9Z9a3XTcQ7kNvwHbSueQ&amp;_nc_oc=AdqZvLfkUECCp-PzosWPpwH6aKcCTcnp5LCTlPaQnAapvNYk3h0vr0MwYZ74N6JJE60&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIIaHm-ZLLeWqyzE87P30_-cNCHO9sQVloN5bT3aFotpg&amp;oe=6AB395EC; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/720495745_3377270445780693_888169211609445957_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PEd1aWG90c4Q7kNvwFfUOQ4&amp;_nc_oc=AdrTRXfrx1pomRzcompzkQAMeyuhMDOb6GxUxdzedExILCEZNRNmCOswHKYdYi-vFpY&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQJdSmbYZUx1bo6s6BUqTCImTGV2rJasH5LeKQDXXFya1A&amp;oe=6AB3A127</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>rv amazon find</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>amazon find</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>104</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/791791057</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>You guys were so helpful when I asked for advice so I thought I’d share a few of my “hacks” to maybe help someone else! ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_791791057\img_1.jpg; data\images\amazon_find_791791057\img_2.jpg; data\images\amazon_find_791791057\img_3.jpg; data\images\amazon_find_791791057\img_4.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Public Search</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>791791057</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/718204993_3377270389114032_3017451080494617445_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=qYfYw4OVFlQQ7kNvwFzTUw2&amp;_nc_oc=AdrTdokM1V_C9TzLfjq5_yhdW9z1pnNrXAPOqM7sMo9zBm1IgAoSMyik8zLi5QctYCQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQKN6mRZQV1JOvOk5cGH3-J9bLpZnNAF30D41_tiHhRwqA&amp;oe=6AB393CE; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/719160410_3377257819115289_4512916211874135718_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx960x720&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=kme4VsbYGiQQ7kNvwF0UTnh&amp;_nc_oc=AdpLFsFTOQlfY2GtWNtHZkgfNauVxu3L28i1m9bTX7UjZW46L_6uJXsumd63ry3hM_E&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIpFVodpDrLXaNrm03MWNxcRUQTUe0bD15QwfGTs15G_A&amp;oe=6AB39474; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715749899_3377270385780699_46444169963824531_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=m1B9Z9a3XTcQ7kNvwHbSueQ&amp;_nc_oc=AdqZvLfkUECCp-PzosWPpwH6aKcCTcnp5LCTlPaQnAapvNYk3h0vr0MwYZ74N6JJE60&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIIaHm-ZLLeWqyzE87P30_-cNCHO9sQVloN5bT3aFotpg&amp;oe=6AB395EC; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/720495745_3377270445780693_888169211609445957_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PEd1aWG90c4Q7kNvwFfUOQ4&amp;_nc_oc=AdrTRXfrx1pomRzcompzkQAMeyuhMDOb6GxUxdzedExILCEZNRNmCOswHKYdYi-vFpY&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQJdSmbYZUx1bo6s6BUqTCImTGV2rJasH5LeKQDXXFya1A&amp;oe=6AB3A127</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="P21" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B22" t="n">
         <v>80</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C22" t="n">
         <v>92</v>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3583318008493819/</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>It's level, but still wobbles when walking inside.
 Can you knowledgeable friends tell me what you think of our set up. We've heard that not lowering the stabilizers all the way helps with the wobble.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>data\images\hack_3583318008493819\img_1.jpg; data\images\hack_3583318008493819\img_2.jpg; data\images\hack_3583318008493819\img_3.jpg</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J22" t="n">
         <v>3583318008493819</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/763072132_10240527915834058_262860686266165320_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tQPKb_7z3scQ7kNvwHI1W7g&amp;_nc_oc=AdryOCOHLUetXqxLh_YB0dln50lhK5trI90T_Fm1qocc_zcSjKjM7rFYwajXvgsjhTI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJ0GnPf57poAwnS1tveFqIifG41xCwgcTXoj7nwXsPD0g&amp;oe=6AB39330; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/764719882_10240527916554076_6179174592261675065_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGePznIup-IQ7kNvwF8n1gs&amp;_nc_oc=AdpGktVoydqk0AxdQDAOzbx_Pf2MDjo3DIQObD1Zjm6Y7VQBbann44VUTt2JZv16NT8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJvlQLTekeLpX0VeuXsY7AW8BTlFEb4ontl07T28WmncA&amp;oe=6AB39768; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/762276276_10240527918834133_6935526286052437077_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=LUYt4ZPtFlQQ7kNvwFtDGTf&amp;_nc_oc=Ados7w7e5WTUF89zeazhrONFUSOjfR3KkU-WEt4FzNzv3RCM9gJpPLl89FV5RIzy0P4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQIUbRAOYKraspj5sBL0vF-0I_3MUiK5eLiusqFF-B6VQQ&amp;oe=6AB3908B</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>rv stabilizer x chock</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="P22" t="n">
         <v>91</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>80</v>
+      </c>
+      <c r="C23" t="n">
+        <v>92</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3583318008493819/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>It's level, but still wobbles when walking inside.
+Can you knowledgeable friends tell me what you think of our set up. We've heard that not lowering the stabilizers all the way helps with the wobble.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>data\images\hack_3583318008493819\img_1.jpg; data\images\hack_3583318008493819\img_2.jpg; data\images\hack_3583318008493819\img_3.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3583318008493819</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/763072132_10240527915834058_262860686266165320_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tQPKb_7z3scQ7kNvwHI1W7g&amp;_nc_oc=AdryOCOHLUetXqxLh_YB0dln50lhK5trI90T_Fm1qocc_zcSjKjM7rFYwajXvgsjhTI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJ0GnPf57poAwnS1tveFqIifG41xCwgcTXoj7nwXsPD0g&amp;oe=6AB39330; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/764719882_10240527916554076_6179174592261675065_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGePznIup-IQ7kNvwF8n1gs&amp;_nc_oc=AdpGktVoydqk0AxdQDAOzbx_Pf2MDjo3DIQObD1Zjm6Y7VQBbann44VUTt2JZv16NT8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJvlQLTekeLpX0VeuXsY7AW8BTlFEb4ontl07T28WmncA&amp;oe=6AB39768; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/762276276_10240527918834133_6935526286052437077_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=LUYt4ZPtFlQQ7kNvwFtDGTf&amp;_nc_oc=Ados7w7e5WTUF89zeazhrONFUSOjfR3KkU-WEt4FzNzv3RCM9gJpPLl89FV5RIzy0P4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQIUbRAOYKraspj5sBL0vF-0I_3MUiK5eLiusqFF-B6VQQ&amp;oe=6AB3908B</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>rv stabilizer x chock</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>must have gadget</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B24" t="n">
         <v>71</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C24" t="n">
         <v>176</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/2519590198174784/</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Hi all my husband and I bought our first ever brand new 2021 hideout! With one slideout! We bought it in April of this year! We were loving it so much, it was my dream ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_2519590198174784\img_1.jpg</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>2519590198174784</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/489965465_10161600930962880_4833098666534324521_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1504x2015&amp;ctp=p526x296&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=536f4a&amp;_nc_ohc=xMIVUG5htDkQ7kNvwG8ehE-&amp;_nc_oc=Adp4sJx_jBWQxqAezLmKNS9_5TDHX2yXRWxyb3DDrZ3-anVVRKHC96Jtv_1gNntBUhE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKdYBPNRTeYp1FOp6-rBTffCUwYr55-PcsfEHer1NRGrw&amp;oe=6AB3994F</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>71</v>
+      </c>
+      <c r="C25" t="n">
+        <v>176</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/2519590198174784/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hi all my husband and I bought our first ever brand new 2021 hideout! With one slideout! We bought it in April of this year! We were loving it so much, it was my dream ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_2519590198174784\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>2519590198174784</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/489965465_10161600930962880_4833098666534324521_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1504x2015&amp;ctp=p526x296&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=536f4a&amp;_nc_ohc=xMIVUG5htDkQ7kNvwG8ehE-&amp;_nc_oc=Adp4sJx_jBWQxqAezLmKNS9_5TDHX2yXRWxyb3DDrZ3-anVVRKHC96Jtv_1gNntBUhE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKdYBPNRTeYp1FOp6-rBTffCUwYr55-PcsfEHer1NRGrw&amp;oe=6AB3994F</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="P25" t="n">
         <v>89</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B26" t="n">
         <v>54</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C26" t="n">
         <v>69</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3513687305456890/</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Hello everybody! 
 New, full time rv living here! 
@@ -1283,52 +2035,120 @@
 We have dehumidifiers, keep the window shades down and the windows are factory tinted (we will be putting darker tint on the windows soon). ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>data\images\hack_3513687305456890\img_1.jpg; data\images\hack_3513687305456890\img_2.jpg</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J26" t="n">
         <v>3513687305456890</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>54</v>
+      </c>
+      <c r="C27" t="n">
+        <v>69</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3513687305456890/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Hello everybody! 
+New, full time rv living here! 
+We live in Texas and this heat is getting to us 
+With all 3 ac running it stays about 74 in the camper, which is fine. But hits up to 80 in the bedroom. What's yalls best tips and tricks to keeping the heat down without frying our ac units? 
+We have dehumidifiers, keep the window shades down and the windows are factory tinted (we will be putting darker tint on the windows soon). ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>data\images\hack_3513687305456890\img_1.jpg; data\images\hack_3513687305456890\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3513687305456890</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>rv small dehumidifier</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>amazon find</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B28" t="n">
         <v>46</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C28" t="n">
         <v>47</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/2956335967833536/</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>We are getting ready to PCS soon and will be staying in our camper for about 6 weeks. I have 3 kids (7,4,&amp;2) 
 I’m struggling to find a good “baby proof” way to keep the doors closed. 
@@ -1336,1052 +2156,2066 @@
 Any suggestions on good locks? ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>data\images\amazon_find_2956335967833536\img_1.jpg</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>2956335967833536</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/486263063_3431305033666747_2774947844339664550_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_V3lAOuS71gQ7kNvwG1HA6t&amp;_nc_oc=Ado0M-qFkVhQnVlLURz25aP5SNH_jAdpe4Dmc4HtVTUByPMy0vPdcFtq1ganZeRHiEc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQK8ZOwXZcwYIiJ5OsCjs7fTQm9bTUEleRwYHx_4DZJBiw&amp;oe=6AB39B39</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>إكسسوارات وأدوات تجارية (Commercial Gear &amp; Accessories)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>rv amazon find</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>amazon find</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>46</v>
+      </c>
+      <c r="C29" t="n">
+        <v>47</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/2956335967833536/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>We are getting ready to PCS soon and will be staying in our camper for about 6 weeks. I have 3 kids (7,4,&amp;2) 
+I’m struggling to find a good “baby proof” way to keep the doors closed. 
+The last time we went camping the 2 year old opened the door in the middle of the night. 
+Any suggestions on good locks? ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_2956335967833536\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>2956335967833536</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/486263063_3431305033666747_2774947844339664550_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_V3lAOuS71gQ7kNvwG1HA6t&amp;_nc_oc=Ado0M-qFkVhQnVlLURz25aP5SNH_jAdpe4Dmc4HtVTUByPMy0vPdcFtq1ganZeRHiEc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQK8ZOwXZcwYIiJ5OsCjs7fTQm9bTUEleRwYHx_4DZJBiw&amp;oe=6AB39B39</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="P29" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B30" t="n">
         <v>40</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C30" t="n">
         <v>85</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/4219763604824093/</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Unfortunately, we purchased a 2021 Salem Cruise Lite 282QBXL in June and it has been nothing but trouble since. 
 On our first trip, the slide out wouldn’t retract all the way on its own (yes, I checked it prior to purchase and it seemed to work fine, but looking back, I think they had it jacked up on that side to help assist it and I just thought the driveway was pitched). It would get about a foot out and come to a stop. If I had it jacked up slightly and leaned into it, I ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>data\images\recommendation_4219763604824093\img_1.jpg</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J30" t="n">
         <v>4219763604824093</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>40</v>
+      </c>
+      <c r="C31" t="n">
+        <v>85</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4219763604824093/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Unfortunately, we purchased a 2021 Salem Cruise Lite 282QBXL in June and it has been nothing but trouble since. 
+On our first trip, the slide out wouldn’t retract all the way on its own (yes, I checked it prior to purchase and it seemed to work fine, but looking back, I think they had it jacked up on that side to help assist it and I just thought the driveway was pitched). It would get about a foot out and come to a stop. If I had it jacked up slightly and leaned into it, I ... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_4219763604824093\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>4219763604824093</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>amazon find</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B32" t="n">
         <v>34</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C32" t="n">
         <v>115</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/4228244110642709/</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>My stinky slinky won’t fit in the bumper tubing. Any ideas?</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>data\images\amazon_find_4228244110642709\img_1.jpg</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>4228244110642709</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/789447152_10244813111573647_47739271540443468_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx720x1280&amp;ctp=p526x296&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9RQ21jppgcUQ7kNvwHOPHq-&amp;_nc_oc=AdpS_m5-K5_RU2sUwoQJWJrY-sl4KHrcU30zbIzSrUQ3R25NJhL2uHJx88ZWQYW0umU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKmJVCGhzzaIOrLJSB17QoEwCChxJioCHSDOxuyqiFvMA&amp;oe=6AB3A606</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>تنظيم وتخزين جاهز (Storage &amp; Organization)</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>rv amazon find</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>amazon find</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>34</v>
+      </c>
+      <c r="C33" t="n">
+        <v>115</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4228244110642709/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>My stinky slinky won’t fit in the bumper tubing. Any ideas?</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_4228244110642709\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>4228244110642709</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/789447152_10244813111573647_47739271540443468_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx720x1280&amp;ctp=p526x296&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9RQ21jppgcUQ7kNvwHOPHq-&amp;_nc_oc=AdpS_m5-K5_RU2sUwoQJWJrY-sl4KHrcU30zbIzSrUQ3R25NJhL2uHJx88ZWQYW0umU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKmJVCGhzzaIOrLJSB17QoEwCChxJioCHSDOxuyqiFvMA&amp;oe=6AB3A606</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>تنظيم وتخزين (Storage &amp; Organization)</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="P33" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>must have gadget</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B34" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C34" t="n">
         <v>36</v>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/3605957036204756/</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Soo I want to paint the walls in my camper and I was wondering is there a certain paint or way to go about doing this? Below is what my walls look like in my camper.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_3605957036204756\img_1.jpg</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>3605957036204756</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/514417036_24232386396387276_8898425086872934580_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=0WuEyVKJSqkQ7kNvwGxzTrJ&amp;_nc_oc=AdpwYEulmgEEsjJgMkkuOg0h0LPQX5Bi_s7roUkZ1JKXJsLZhWL2MrHLy_UyPk1-mPA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKl3JPpvV7FsczmsCXiMGk3JcjuvjpM0ztQZBAozZpITg&amp;oe=6AB3CB59</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>must have gadget</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" t="n">
+        <v>36</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3605957036204756/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Soo I want to paint the walls in my camper and I was wondering is there a certain paint or way to go about doing this? Below is what my walls look like in my camper.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>data\images\must_have_gadget_3605957036204756\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3605957036204756</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/514417036_24232386396387276_8898425086872934580_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=0WuEyVKJSqkQ7kNvwGxzTrJ&amp;_nc_oc=AdpwYEulmgEEsjJgMkkuOg0h0LPQX5Bi_s7roUkZ1JKXJsLZhWL2MrHLy_UyPk1-mPA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKl3JPpvV7FsczmsCXiMGk3JcjuvjpM0ztQZBAozZpITg&amp;oe=6AB3CB59</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="P35" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B36" t="n">
         <v>21</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C36" t="n">
         <v>75</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/4242996285834158/</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Question for the elite in this group. If I left the camper plugged in to shore power at home for weeks/months continuously in order to have 110V power. (Dehumidifier) Do y'all feel this will have a wear and tear effect on the converter that I could otherwise avoid by other means?</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J36" t="n">
         <v>4242996285834158</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B37" t="n">
+        <v>21</v>
+      </c>
+      <c r="C37" t="n">
+        <v>75</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4242996285834158/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Question for the elite in this group. If I left the camper plugged in to shore power at home for weeks/months continuously in order to have 110V power. (Dehumidifier) Do y'all feel this will have a wear and tear effect on the converter that I could otherwise avoid by other means?</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4242996285834158</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
         <v>19</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C38" t="n">
         <v>55</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3581840501974903/</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>So our refrigerator just went out in our RV. It’s a Norcold. We are full timers. We also had a mobile RV mechanic come check it. I’m wondering what experience others have had with putting in a regular residential fridge. We never boon dock so the propane option is worthless to us. Our mechanic told us we may have to take out the drawer underneath but we’re fine with that. Just wondering who else has put a regular residential fridge in... عرض المزيد</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3581840501974903</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>19</v>
+      </c>
+      <c r="C39" t="n">
+        <v>55</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3581840501974903/</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>So our refrigerator just went out in our RV. It’s a Norcold. We are full timers. We also had a mobile RV mechanic come check it. I’m wondering what experience others have had with putting in a regular residential fridge. We never boon dock so the propane option is worthless to us. Our mechanic told us we may have to take out the drawer underneath but we’re fine with that. Just wondering who else has put a regular residential fridge in... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
         <v>3581840501974903</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B40" t="n">
         <v>18</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C40" t="n">
         <v>173</v>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/4244102009056919/</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>What is a good space heater to use in a camper?</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J40" t="n">
         <v>4244102009056919</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B41" t="n">
+        <v>18</v>
+      </c>
+      <c r="C41" t="n">
+        <v>173</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4244102009056919/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>What is a good space heater to use in a camper?</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4244102009056919</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
         <v>15</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C42" t="n">
         <v>39</v>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3622362671256019/</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Thoughts….when parked at home  I keep my Class C plugged into shore power all the time.(months at a time) Is there any benefit to unplugging and letting the batteries work a little and then plugging in the charge them up?</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3622362671256019</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>15</v>
+      </c>
+      <c r="C43" t="n">
+        <v>39</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3622362671256019/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Thoughts….when parked at home  I keep my Class C plugged into shore power all the time.(months at a time) Is there any benefit to unplugging and letting the batteries work a little and then plugging in the charge them up?</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
         <v>3622362671256019</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B44" t="n">
         <v>12</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C44" t="n">
         <v>26</v>
       </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3628769393948680/</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J44" t="n">
         <v>3628769393948680</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>غير مؤكد (نقاش عام)</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B45" t="n">
+        <v>12</v>
+      </c>
+      <c r="C45" t="n">
+        <v>26</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3628769393948680/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3628769393948680</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>غير مؤكد (نقاش عام)</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
         <v>9</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C46" t="n">
         <v>32</v>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/3218284608305336/</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Does anyone have a great recommendation for a sofa with a pull out bed? There’s a lot of options for the kind that allows the sofa back to flatten, but it looks like we would have to pull it out from the wall every night. Probably the same for a futon. I would like it to be as simple as possible. It also needs to be comfortable. It will be used full time. 
 Thank you!</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3218284608305336</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" t="n">
+        <v>32</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3218284608305336/</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Does anyone have a great recommendation for a sofa with a pull out bed? There’s a lot of options for the kind that allows the sofa back to flatten, but it looks like we would have to pull it out from the wall every night. Probably the same for a futon. I would like it to be as simple as possible. It also needs to be comfortable. It will be used full time. 
+Thank you!</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
         <v>3218284608305336</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B48" t="n">
         <v>8</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C48" t="n">
         <v>55</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3629156827243270/</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Okay, y’all…we officially did a thing!
 My husband and I just bought our first camper — a 2022 Cherokee Grey Wolf Limited 27RR — and we are COMPLETE newbies to the camping world. We’ve always enjoyed getting away, but this is our first time actually owning a camper, so I’m about to learn A LOT.
 We also have a Can-Am Defender that we can haul in the toy hauler, although we’ll probably use it more for hunting trips than camping.... عرض المزيد</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J48" t="n">
         <v>3629156827243270</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B49" t="n">
         <v>8</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C49" t="n">
         <v>48</v>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J49" t="n">
         <v>3359003754258580</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>amazon find</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B50" t="n">
         <v>8</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C50" t="n">
         <v>32</v>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>data\images\amazon_find_4147910648676056\img_1.jpg</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>4147910648676056</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKuI7NhSiWUW3pweIYcuSccGm2fBiXhQmnukqpjQKDiRg&amp;oe=6AB3C7D6</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="M50" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>rv 12v portable bunk fan</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" t="n">
+        <v>48</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>3359003754258580</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" t="n">
+        <v>32</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>data\images\hack_4147910648676056\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>4147910648676056</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>rv 12v portable bunk fan</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="P52" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>8</v>
+      </c>
+      <c r="C53" t="n">
+        <v>55</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3629156827243270/</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Okay, y’all…we officially did a thing!
+My husband and I just bought our first camper — a 2022 Cherokee Grey Wolf Limited 27RR — and we are COMPLETE newbies to the camping world. We’ve always enjoyed getting away, but this is our first time actually owning a camper, so I’m about to learn A LOT.
+We also have a Can-Am Defender that we can haul in the toy hauler, although we’ll probably use it more for hunting trips than camping.... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3629156827243270</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" t="n">
+        <v>36</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>3617867058372247</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" t="n">
+        <v>34</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>3128604820606649</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="n">
+        <v>36</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>3617867058372247</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" t="n">
+        <v>34</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>3128604820606649</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>43</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3631536470338639/</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Need recommendation for a new mattress! Prefer medium firm!</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>3631536470338639</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" t="n">
+        <v>43</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3631536470338639/</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Need recommendation for a new mattress! Prefer medium firm!</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>3631536470338639</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>8</v>
-      </c>
-      <c r="C28" t="n">
-        <v>32</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>data\images\hack_4147910648676056\img_1.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>4147910648676056</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>rv 12v portable bunk fan</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>34</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>3128604820606649</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>7</v>
-      </c>
-      <c r="C30" t="n">
-        <v>36</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>3617867058372247</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>غير مؤهل (بدون صور)</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="n">
-        <v>43</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3631536470338639/</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Need recommendation for a new mattress! Prefer medium firm!</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>3631536470338639</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>غير مؤهل (بدون صور)</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+      <c r="B60" t="n">
         <v>3</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C60" t="n">
         <v>177</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D60" t="n">
         <v>278</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/2790989414393353/</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>This collapsible pet pool from Aldi fits perfectly in the neo angle shower. Might be useful for those of you with pets or kiddos who would like a bath. They sell them on amazon too.
 Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J60" t="n">
         <v>2790989414393353</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="M60" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>rv collapsible pet pool</t>
         </is>
       </c>
-      <c r="P32" t="n">
+      <c r="P60" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" t="n">
+        <v>177</v>
+      </c>
+      <c r="D61" t="n">
+        <v>278</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/2790989414393353/</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>This collapsible pet pool from Aldi fits perfectly in the neo angle shower. Might be useful for those of you with pets or kiddos who would like a bath. They sell them on amazon too.
+Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2790989414393353</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
         <v>2</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C62" t="n">
         <v>85</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D62" t="n">
         <v>41</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/RVhackcamp/posts/3498835016916959/</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>3498835016916959</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>85</v>
+      </c>
+      <c r="D63" t="n">
+        <v>41</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3498835016916959/</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
         <v>3498835016916959</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>hack</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B64" t="n">
         <v>1</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C64" t="n">
         <v>71</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D64" t="n">
         <v>54</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3080238785468413/</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>It was so annoying I couldn’t put my tailgate all the way down! So flipped this and problem solved !</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J64" t="n">
         <v>3080238785468413</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="M64" t="n">
         <v>1</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>tailgate jack clearance flip</t>
         </is>
       </c>
-      <c r="P34" t="n">
+      <c r="P64" t="n">
         <v>86</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>71</v>
+      </c>
+      <c r="D65" t="n">
+        <v>54</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3080238785468413/</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>It was so annoying I couldn’t put my tailgate all the way down! So flipped this and problem solved !</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3080238785468413</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>tailgate jack clearance flip</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/data/reports/viral_posts.xlsx
+++ b/data/reports/viral_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>winner_score</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>affiliate_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -561,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -572,6 +577,7 @@
       <c r="P2" t="n">
         <v>99</v>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -637,6 +643,7 @@
       <c r="P3" t="n">
         <v>99</v>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -698,6 +705,7 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -761,6 +769,7 @@
       <c r="P5" t="n">
         <v>91</v>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -807,10 +816,23 @@
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>تنظيم وتخزين جاهز (Storage &amp; Organization)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>bunk bed trampoline ladder</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -875,6 +897,7 @@
       <c r="P7" t="n">
         <v>97</v>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -939,6 +962,7 @@
       <c r="P8" t="n">
         <v>89</v>
       </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1001,6 +1025,7 @@
       <c r="P9" t="n">
         <v>89</v>
       </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1056,7 +1081,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1067,6 +1092,7 @@
       <c r="P10" t="n">
         <v>73</v>
       </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1135,6 +1161,7 @@
       <c r="P11" t="n">
         <v>73</v>
       </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1201,6 +1228,7 @@
       <c r="P12" t="n">
         <v>100</v>
       </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1265,6 +1293,7 @@
       <c r="P13" t="n">
         <v>100</v>
       </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1316,7 +1345,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1325,8 +1354,9 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>81</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1391,6 +1421,7 @@
       <c r="P15" t="n">
         <v>73</v>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1456,6 +1487,7 @@
       <c r="P16" t="n">
         <v>81</v>
       </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1519,6 +1551,7 @@
       <c r="P17" t="n">
         <v>81</v>
       </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1565,10 +1598,19 @@
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1629,6 +1671,7 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1693,6 +1736,7 @@
       <c r="P20" t="n">
         <v>83</v>
       </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1755,6 +1799,7 @@
       <c r="P21" t="n">
         <v>91</v>
       </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1807,7 +1852,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1816,8 +1861,9 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>91</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1883,6 +1929,7 @@
       <c r="P23" t="n">
         <v>83</v>
       </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1943,6 +1990,7 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2005,6 +2053,7 @@
       <c r="P25" t="n">
         <v>89</v>
       </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2055,10 +2104,23 @@
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>rv small dehumidifier</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2127,6 +2189,7 @@
       <c r="P27" t="n">
         <v>70</v>
       </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2194,6 +2257,7 @@
       <c r="P28" t="n">
         <v>81</v>
       </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2259,6 +2323,7 @@
       <c r="P29" t="n">
         <v>81</v>
       </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2306,10 +2371,19 @@
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2371,6 +2445,7 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2435,6 +2510,7 @@
       <c r="P32" t="n">
         <v>81</v>
       </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2497,6 +2573,7 @@
       <c r="P33" t="n">
         <v>81</v>
       </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2557,6 +2634,7 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2619,6 +2697,7 @@
       <c r="P35" t="n">
         <v>81</v>
       </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2669,6 +2748,7 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2721,6 +2801,7 @@
       <c r="P37" t="n">
         <v>0</v>
       </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2773,6 +2854,7 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2815,6 +2897,7 @@
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2865,6 +2948,7 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2917,6 +3001,7 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2969,6 +3054,7 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3011,6 +3097,7 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3069,6 +3156,7 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3129,6 +3217,7 @@
       <c r="P45" t="n">
         <v>0</v>
       </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3182,6 +3271,7 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3233,6 +3323,7 @@
       <c r="P47" t="n">
         <v>0</v>
       </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3244,267 +3335,280 @@
         <v>8</v>
       </c>
       <c r="C48" t="n">
+        <v>48</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>3359003754258580</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="n">
+        <v>32</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>data\images\hack_4147910648676056\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>4147910648676056</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>rv 12v portable bunk fan</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>amazon find</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" t="n">
+        <v>32</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_4147910648676056\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>4147910648676056</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKuI7NhSiWUW3pweIYcuSccGm2fBiXhQmnukqpjQKDiRg&amp;oe=6AB3C7D6</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>rv 12v portable bunk fan</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" t="n">
+        <v>48</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>3359003754258580</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" t="n">
         <v>55</v>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/roadtreking/posts/3629156827243270/</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Okay, y’all…we officially did a thing!
 My husband and I just bought our first camper — a 2022 Cherokee Grey Wolf Limited 27RR — and we are COMPLETE newbies to the camping world. We’ve always enjoyed getting away, but this is our first time actually owning a camper, so I’m about to learn A LOT.
 We also have a Can-Am Defender that we can haul in the toy hauler, although we’ll probably use it more for hunting trips than camping.... عرض المزيد</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>3629156827243270</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>غير مؤهل (بدون صور)</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>8</v>
-      </c>
-      <c r="C49" t="n">
-        <v>48</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>3359003754258580</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>amazon find</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>8</v>
-      </c>
-      <c r="C50" t="n">
-        <v>32</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>data\images\amazon_find_4147910648676056\img_1.jpg</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>4147910648676056</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKuI7NhSiWUW3pweIYcuSccGm2fBiXhQmnukqpjQKDiRg&amp;oe=6AB3C7D6</t>
-        </is>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>rv 12v portable bunk fan</t>
-        </is>
-      </c>
-      <c r="P50" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" t="n">
-        <v>48</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>3359003754258580</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>غير مؤهل (بدون صور)</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>8</v>
-      </c>
-      <c r="C52" t="n">
-        <v>32</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>data\images\hack_4147910648676056\img_1.jpg</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>RVhackcamp</t>
+          <t>roadtreking</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>4147910648676056</v>
+        <v>3629156827243270</v>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>rv 12v portable bunk fan</t>
-        </is>
-      </c>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>81</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3559,6 +3663,7 @@
       <c r="P53" t="n">
         <v>0</v>
       </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3570,30 +3675,30 @@
         <v>7</v>
       </c>
       <c r="C54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
+          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>roadtreking</t>
+          <t>RVhackcamp</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>3617867058372247</v>
+        <v>3128604820606649</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3609,6 +3714,7 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3620,37 +3726,46 @@
         <v>7</v>
       </c>
       <c r="C55" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/3128604820606649/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3617867058372247/</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Looking for campground recommendations for Corpus Christi, TX.</t>
+          <t>Hello, has anyone ever paid to have someone move their RV from one state to another? I was looking online but now I have been bombarded by different companies. Just hoping to hear if someone has used one. ￼</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>RVhackcamp</t>
+          <t>roadtreking</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>3128604820606649</v>
+        <v>3617867058372247</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3703,6 +3818,7 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3755,6 +3871,7 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3807,6 +3924,7 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3857,6 +3975,7 @@
       <c r="P59" t="n">
         <v>0</v>
       </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3905,21 +4024,18 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>rv collapsible pet pool</t>
-        </is>
-      </c>
+          <t>استبعاد (نقاش/سفر/شكوى)</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3981,6 +4097,7 @@
       <c r="P61" t="n">
         <v>0</v>
       </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4041,6 +4158,7 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4091,6 +4209,7 @@
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4142,7 +4261,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4151,8 +4270,9 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>86</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4217,6 +4337,7 @@
       <c r="P65" t="n">
         <v>70</v>
       </c>
+      <c r="Q65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/reports/viral_posts.xlsx
+++ b/data/reports/viral_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,55 +461,60 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>generated_caption</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>local_images</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>author</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>group_id</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>post_id</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>image_urls</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>is_product</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>product_category</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>amazon_query</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>winner_score</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>affiliate_url</t>
         </is>
@@ -543,41 +548,47 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Honestly didn't expect rv must have gadget to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>data\images\must_have_gadget_4124414001025721\img_1.jpg; data\images\must_have_gadget_4124414001025721\img_2.jpg; data\images\must_have_gadget_4124414001025721\img_3.jpg</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>4124414001025721</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/714611806_10215958763359663_6601841730117456563_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1386x2048&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=e1O3zMI2FBAQ7kNvwH0f9kz&amp;_nc_oc=Adrlw0O8ab8aboNq_-Issv4ZciryIkKZBDfmyzFxZiGWadT3Gk3TKsaWld3S8OPoobk&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI4ZelcCflvqEJ2kpSSxWFEzejtqTMDMQQyV93rqWUKtQ&amp;oe=6AB3BC85; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/714384150_10215958763759673_8245354785028741008_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx935x1272&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=FpOY9vQtJ6YQ7kNvwGRrp_C&amp;_nc_oc=AdqVcmZxnd_HmBnrMWMo1IQwxCZhT3KzI9F-kZeoGmuIlDtWr_BOud5c2P1J1ogRNTQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLJppTjdJa-7osH0NPYnAJCp__ERaaJzgRYx4xQGpdzUA&amp;oe=6AB39A9B; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715435401_10215958764119682_4239662220553189837_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x2048&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=Lgyxk1qwPP8Q7kNvwExOJLi&amp;_nc_oc=AdrFTRRleOoNTZXioS5hSn97k-U5pLE8wzdP2Th_-pYVRRRQHaSxcAxUNJWUmBCyl3Y&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKXWP-_umRYvMmKVNdu03tTuOXsQLCnkNnzHA-iQQCm2w&amp;oe=6AB3B4D0</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>99</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -607,43 +618,50 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Our teenager flat-out refused to squeeze into the standard RV bunk until we set this up.
+It turned a tiny, cramped corner into her own cozy private space in less than five minutes. Honestly saved our whole family camping trip!
+I dropped the link in the first comment if you want one 👇</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>data\images\must_have_gadget_4124414001025721\img_1.jpg; data\images\must_have_gadget_4124414001025721\img_2.jpg; data\images\must_have_gadget_4124414001025721\img_3.jpg</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>4124414001025721</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/714611806_10215958763359663_6601841730117456563_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1386x2048&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=e1O3zMI2FBAQ7kNvwH0f9kz&amp;_nc_oc=Adrlw0O8ab8aboNq_-Issv4ZciryIkKZBDfmyzFxZiGWadT3Gk3TKsaWld3S8OPoobk&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI4ZelcCflvqEJ2kpSSxWFEzejtqTMDMQQyV93rqWUKtQ&amp;oe=6AB3BC85; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/714384150_10215958763759673_8245354785028741008_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx935x1272&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=FpOY9vQtJ6YQ7kNvwGRrp_C&amp;_nc_oc=AdqVcmZxnd_HmBnrMWMo1IQwxCZhT3KzI9F-kZeoGmuIlDtWr_BOud5c2P1J1ogRNTQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLJppTjdJa-7osH0NPYnAJCp__ERaaJzgRYx4xQGpdzUA&amp;oe=6AB39A9B; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715435401_10215958764119682_4239662220553189837_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x2048&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=Lgyxk1qwPP8Q7kNvwExOJLi&amp;_nc_oc=AdrFTRRleOoNTZXioS5hSn97k-U5pLE8wzdP2Th_-pYVRRRQHaSxcAxUNJWUmBCyl3Y&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKXWP-_umRYvMmKVNdu03tTuOXsQLCnkNnzHA-iQQCm2w&amp;oe=6AB3B4D0</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>99</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -671,41 +689,42 @@
 We are so happy!!</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>data\images\hack_2389439124523226\img_1.jpg; data\images\hack_2389439124523226\img_2.jpg; data\images\hack_2389439124523226\img_3.jpg; data\images\hack_2389439124523226\img_4.jpg; data\images\hack_2389439124523226\img_5.jpg</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2389439124523226</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -733,43 +752,44 @@
 We are so happy!!</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>data\images\hack_2389439124523226\img_1.jpg; data\images\hack_2389439124523226\img_2.jpg; data\images\hack_2389439124523226\img_3.jpg; data\images\hack_2389439124523226\img_4.jpg; data\images\hack_2389439124523226\img_5.jpg</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>2389439124523226</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439537905141_7744078254309363716_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aBBTZz_R2QQQ7kNvwH6lixB&amp;_nc_oc=AdrDHARpuJPd1FYGMfbWaoFRCYKM68UoRfG2ibtABAbasTot0CRQZOaJ-tsq3z4hwBg&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJPkyXCbdYJpNgWBF9bziSrMSwlVo0YIakXWfqgEwrXJw&amp;oe=6AD55F0B; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189465542_4439538025144_4331371041119588443_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=KbayQGqGrwcQ7kNvwFlrRoi&amp;_nc_oc=AdpEpEsUlvAoi8JLc4pIs1f5SOVBqvi4Pm3eVx7zeZzXdA8uqeXg2rlvBqel-3gkqVU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIuIceKOeu1P6QBrOiEmSKpFEGQBXZvQCoMTZQw_bvZeA&amp;oe=6AD542BC; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/187248079_4439538905166_2897692911484219363_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=Hsd1zRsnrtUQ7kNvwHCNVF0&amp;_nc_oc=AdpkHDrkX41B23eqN97JnQ7_e-0FiKex0OUAcnQ4kC7GgOAyRVIqGhm2dJ13fdumL6s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJhNpn4ODMfW5R59eS_i0Qj61CzeETc7Jl8XQMBU08bRA&amp;oe=6AD54DE9; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189239174_4439538665160_1105640096963475063_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=aQ_AFWigRS0Q7kNvwEm6Wlv&amp;_nc_oc=AdoELA5q9-3ZXPZ-v-HOrHuCoCzgBgw9dTspmR43JLg06-Jjd_0mw6pYPx3F7dipSXw&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQLUjhCUBhH1_IlA3T75xQf_syW9hZRdYJWgHGXkW-YOxw&amp;oe=6AD55CF8; https://scontent.fcai19-4.fna.fbcdn.net/v/t1.6435-9/189573366_4439538465155_4433609016928526357_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx960x960&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=33274f&amp;_nc_ohc=q7E8f_9ooVYQ7kNvwFH7NPn&amp;_nc_oc=AdoqHlvmXZ36vOEywV086n7ThG1SXJfZXcCcsBrMGB03C0jais65-Ei56dleFzvx710&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIwEVuMu05e-pZfNXH7FQtqaJfq2B-xgk1w4vnodfMNkQ&amp;oe=6AD5530E</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>rv hack</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>91</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -798,41 +818,47 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Honestly didn't expect bunk bed trampoline ladder to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>data\images\hack_3308082032658926\img_1.jpg</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>3308082032658926</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>تنظيم وتخزين جاهز (Storage &amp; Organization)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>bunk bed trampoline ladder</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>97</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -861,43 +887,50 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Best $25 camper hack we’ve done so far.
+Our camper didn’t come with a bunk ladder, and my girls kept struggling to climb up. Regular ones were way too tall, but a cheap trampoline ladder hooked right onto the frame.
+I’ll leave the link in the first comment! 👇</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>data\images\hack_3308082032658926\img_1.jpg</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>3308082032658926</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/505610137_10228627949544225_29184265896986180_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QpbI0HISIwUQ7kNvwGpoC3m&amp;_nc_oc=AdpTak13XLuKr-YWRhmqrvQ1Nfw2nkxBsfWn-qQZc0F0aLf_4Q2FFXtFVQaJYuAkZeU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIdd6NLfsBY2RtHLGMrQXjTnSLvFNa0lbB95FHWlJJxeA&amp;oe=6AB39A8F</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>تنظيم وتخزين جاهز (Storage &amp; Organization)</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>bunk bed trampoline ladder</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>97</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -926,43 +959,50 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Honestly, why did no one tell me about this before our last RV trip?
+I used to spend 20 minutes stressing over getting the rig level on uneven ground every time we parked. Got this last week and was fully set up in under two minutes flat.
+I left the link in the first comment if you want it! 👇</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>data\images\must_have_gadget_4009327692534353\img_1.jpg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>4009327692534353</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/643396407_10238655093303438_2982570874296650007_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QvAD0_ZeHdEQ7kNvwHy778z&amp;_nc_oc=AdqBe3rZBJ3X2Tj7tMqgAfl7NMUdiQQd8sMoyfXjYeHH-8ewyBv_yNBoyhPsZucF3yA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIUChpHh0PDussfNot-ZthDMoiDU_kAzhX2nuuDxqd_Xg&amp;oe=6AB3C10F</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>89</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -989,43 +1029,44 @@
           <t>What’s your “why did no one tell me I needed this?” item for camping?... عرض المزيد</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_4009327692534353\img_1.jpg</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>4009327692534353</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/643396407_10238655093303438_2982570874296650007_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=QvAD0_ZeHdEQ7kNvwHy778z&amp;_nc_oc=AdqBe3rZBJ3X2Tj7tMqgAfl7NMUdiQQd8sMoyfXjYeHH-8ewyBv_yNBoyhPsZucF3yA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIUChpHh0PDussfNot-ZthDMoiDU_kAzhX2nuuDxqd_Xg&amp;oe=6AB3C10F</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>89</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1058,41 +1099,47 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Honestly didn't expect rv amazon find to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>data\images\amazon_find_4113730608760727\img_1.jpg</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>4113730608760727</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710710608_3365719276935810_913380809031877934_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1290x1728&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=W4Mx_7udmmcQ7kNvwFJ4xZI&amp;_nc_oc=AdqFT1td-gxh5OjykSM57gmwHH8rg2J4DkAgoVkCftj1D8ioDF6ymqGPV7zwA4SlLIs&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQJVruWyQvhPwbT7S7oAFjSG9T7OumAe5miDQecXxPLwqw&amp;oe=6AB3B1EB</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>73</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1125,43 +1172,50 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Finally figured out how to block that blinding morning sun in our RV.
+I grabbed this cheap blackout vinyl on Amazon, and it completely hides the ugly window frames while keeping the camper pitch black for sleeping in. 
+I left the link in the first comment 👇</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>data\images\amazon_find_4113730608760727\img_1.jpg</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>4113730608760727</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710710608_3365719276935810_913380809031877934_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1290x1728&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=W4Mx_7udmmcQ7kNvwFJ4xZI&amp;_nc_oc=AdqFT1td-gxh5OjykSM57gmwHH8rg2J4DkAgoVkCftj1D8ioDF6ymqGPV7zwA4SlLIs&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQJVruWyQvhPwbT7S7oAFjSG9T7OumAe5miDQecXxPLwqw&amp;oe=6AB3B1EB</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>73</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1192,43 +1246,49 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Honestly didn't expect rv hanging shoe organizer to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>data\images\must_have_gadget_177043908\img_1.jpg; data\images\must_have_gadget_177043908\img_2.jpg; data\images\must_have_gadget_177043908\img_3.jpg; data\images\must_have_gadget_177043908\img_4.jpg; data\images\must_have_gadget_177043908\img_5.jpg</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Public Search</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>177043908</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655900116_26426801810294266_616338587343076791_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=jB-xL4WCwAgQ7kNvwFsIIDC&amp;_nc_oc=AdoGV6P4nAjOyR8A4bqzpg8FsSFsTzuA9J9oYzN3nvHnZSZOlC6sXJaEQPLvrs9zuXc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLUYw_U16e1OluoKTx7qceTxgRUASaIWKPWYSNAPF7z1w&amp;oe=6AB3AB8A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/656840747_26426801883627592_1775700405554872607_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=j8NFBjoOyBgQ7kNvwGMUo7s&amp;_nc_oc=AdqOeMpnaO7GTgDmhNWFl03ZZ_QL7ZHss7jWCq2a7ZYSMXuKGE1WUJ9CfjqRoFvo9eU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQJRDiTDfLxEoM8Xrvq6SX0XMQ3iNan62a_aWFxF6SNbTQ&amp;oe=6AB3A8C1; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657150247_26426801800294267_4229617446844769500_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5uBeSm0hyV4Q7kNvwH9eak5&amp;_nc_oc=AdqD-e9fhg29P5ptbb-bxoATLpJLzKa5ChpOU3XznPSRGg45TbRqnGiekZ-Fj2fFdn0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQKg6QyAcUm2tguTzAJn5IZvx9Qg5619GpKKp-wmYaZQRQ&amp;oe=6AB3A834; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654788918_26426801906960923_9152926241027148999_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4RIBSqLMeMwQ7kNvwHiyBp2&amp;_nc_oc=AdoFw7HCp0WiCNPFdtTg_qOn24YtaAUsamWcP_0v6RFoomJsna8Gnk8_8s_weRijukI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLX2ScQA5L21ZhRwZqfvML7zcU4HXflbHCENha7umNhbw&amp;oe=6AB3BD78; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657400660_26426801690294278_6323538386743307505_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=UVxsV1XnU1YQ7kNvwH4wdgb&amp;_nc_oc=AdoRtrvoNkiOrIL8az4oODToaK-5CuEH5v8d56ZqqHZ8_rABt700zdiT_V3Zsx3XWtI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQK1Agtjk-e11HuLDvO8Mo64I7XyMomEEkyGgv6D6jwABQ&amp;oe=6AB399F0</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>تنظيم وتخزين جاهز (Storage &amp; Organization)</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>rv hanging shoe organizer</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1257,43 +1317,44 @@
 As for laundry bag thing on wall, after testing it out this last week... ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_177043908\img_1.jpg; data\images\must_have_gadget_177043908\img_2.jpg; data\images\must_have_gadget_177043908\img_3.jpg; data\images\must_have_gadget_177043908\img_4.jpg; data\images\must_have_gadget_177043908\img_5.jpg</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Public Search</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>177043908</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655900116_26426801810294266_616338587343076791_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=jB-xL4WCwAgQ7kNvwFsIIDC&amp;_nc_oc=AdoGV6P4nAjOyR8A4bqzpg8FsSFsTzuA9J9oYzN3nvHnZSZOlC6sXJaEQPLvrs9zuXc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLUYw_U16e1OluoKTx7qceTxgRUASaIWKPWYSNAPF7z1w&amp;oe=6AB3AB8A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/656840747_26426801883627592_1775700405554872607_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=j8NFBjoOyBgQ7kNvwGMUo7s&amp;_nc_oc=AdqOeMpnaO7GTgDmhNWFl03ZZ_QL7ZHss7jWCq2a7ZYSMXuKGE1WUJ9CfjqRoFvo9eU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQJRDiTDfLxEoM8Xrvq6SX0XMQ3iNan62a_aWFxF6SNbTQ&amp;oe=6AB3A8C1; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657150247_26426801800294267_4229617446844769500_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5uBeSm0hyV4Q7kNvwH9eak5&amp;_nc_oc=AdqD-e9fhg29P5ptbb-bxoATLpJLzKa5ChpOU3XznPSRGg45TbRqnGiekZ-Fj2fFdn0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQKg6QyAcUm2tguTzAJn5IZvx9Qg5619GpKKp-wmYaZQRQ&amp;oe=6AB3A834; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654788918_26426801906960923_9152926241027148999_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4RIBSqLMeMwQ7kNvwHiyBp2&amp;_nc_oc=AdoFw7HCp0WiCNPFdtTg_qOn24YtaAUsamWcP_0v6RFoomJsna8Gnk8_8s_weRijukI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQLX2ScQA5L21ZhRwZqfvML7zcU4HXflbHCENha7umNhbw&amp;oe=6AB3BD78; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/657400660_26426801690294278_6323538386743307505_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx736x1000&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=UVxsV1XnU1YQ7kNvwH4wdgb&amp;_nc_oc=AdoRtrvoNkiOrIL8az4oODToaK-5CuEH5v8d56ZqqHZ8_rABt700zdiT_V3Zsx3XWtI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=UnTMyOwTXyTerwvTKQdb8A&amp;_nc_ss=7b2a8&amp;oh=00_AQK1Agtjk-e11HuLDvO8Mo64I7XyMomEEkyGgv6D6jwABQ&amp;oe=6AB399F0</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>تنظيم وتخزين (Storage &amp; Organization)</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>rv hanging shoe organizer</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>100</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1322,41 +1383,47 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>Honestly didn't expect rv stabilizer x chock to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>data\images\hack_3353573731443089\img_1.jpg</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>3353573731443089</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>rv stabilizer x chock</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>73</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1385,43 +1452,50 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>I finally stopped our camper from shaking every time the kids rolled over in their sleep.
+We tried regular jacks, but the tires were still bouncing. Locking these X-chocks between the wheels completely stopped the sway. I actually slept through the night for once!
+I left the link in the first comment 👇</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>data\images\hack_3353573731443089\img_1.jpg</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>3353573731443089</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/509315519_10236268302438546_5627664025545909431_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=M5yo1ydhuAIQ7kNvwFkGTxw&amp;_nc_oc=Adqlt4_mY-0WuZ0hLNgWsv01h-8e_UMZoRjTxZB7R1aPTqNOGMIVqU4-jG-oot5D2js&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQJz7r6i1K_Fsbm4nFS6qBE0tcL1ZpMwxlZa5XalCv-lgQ&amp;oe=6AB3A54C</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>rv stabilizer x chock</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>73</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1451,43 +1525,50 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Honest question: why do stock RV water heaters only last 90 seconds? 😅
+We used to freeze halfway through every single shower. Snagged this compact tankless heater last month and now we get endless hot water at every campsite. Total lifesaver for family trips.
+I left the link in the first comment 👇</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>data\images\must_have_gadget_3339400259527103\img_1.jpg</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>3339400259527103</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/504466196_30951392407793645_1083003521996665110_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PKBd6m8794QQ7kNvwHv6k2T&amp;_nc_oc=AdqXfd2GEhQ2tfaXL2IkQ5e03U05M1IagmAMktvw6im0SvIyX2X0BXBusblw6qbLA9Q&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI0GDL8YgVHTfZhhbmWGQfWuXOAXKGlyQLPLfy17BdcbA&amp;oe=6AB397B0</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>81</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1515,43 +1596,44 @@
 . We are newbies at camping. We are camping for our second time and we have hot water but it doesn't last long. We DIDNT have this switch on and the water was very hot but didn't even last one shower. Does this switch do something to make the hot water last longer? We are at a full hook up site. Coachmen Catalina legacy camper.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_3339400259527103\img_1.jpg</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>3339400259527103</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/504466196_30951392407793645_1083003521996665110_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PKBd6m8794QQ7kNvwHv6k2T&amp;_nc_oc=AdqXfd2GEhQ2tfaXL2IkQ5e03U05M1IagmAMktvw6im0SvIyX2X0BXBusblw6qbLA9Q&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=1eCUd6gOywCURufMd_fVdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQI0GDL8YgVHTfZhhbmWGQfWuXOAXKGlyQLPLfy17BdcbA&amp;oe=6AB397B0</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>81</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1578,39 +1660,40 @@
           <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>3845725655561225</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1637,41 +1720,42 @@
           <t>Has anyone ever had any luck with a manufacturers buy back on a new camper? Bought this camper right at a year ago. It’s a 2025 forest river sierra 3800rk. Purchased camper from Rocky Ridge Rv in Van Buren Arkansas (save yourself the hassle and avoid these lying fools) shortly after getting the camper we noticed it was deteriorating quickly. Things separating from the walls such as the waterfall table and our shower had a huge gap between it and the wall, camper wouldn’t leve... عرض المزيد</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>data\images\recommendation_3845725655561225\img_1.jpg</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>3845725655561225</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/561728600_3814124955386211_4597581507350432745_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_H-ynFA0RAEQ7kNvwH652sw&amp;_nc_oc=AdpptTd6DXG4EzDKLZRyUHLG9uCQs_nhT9UV9cTPScoYyv5t3AObH6jdhgh-FP11MNA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A1RxZp9G0O8HLhEwpESXLA&amp;_nc_ss=7b2a8&amp;oh=00_AQJSpLc0DrAVWqgXHb9V1F8w2ojb5rgvV8cZ00Tsu2I1oA&amp;oe=6AB3C1B8</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1700,43 +1784,49 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>Honestly didn't expect rv amazon find to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>data\images\amazon_find_791791057\img_1.jpg; data\images\amazon_find_791791057\img_2.jpg; data\images\amazon_find_791791057\img_3.jpg; data\images\amazon_find_791791057\img_4.jpg</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Public Search</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>791791057</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/718204993_3377270389114032_3017451080494617445_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=qYfYw4OVFlQQ7kNvwFzTUw2&amp;_nc_oc=AdrTdokM1V_C9TzLfjq5_yhdW9z1pnNrXAPOqM7sMo9zBm1IgAoSMyik8zLi5QctYCQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQKN6mRZQV1JOvOk5cGH3-J9bLpZnNAF30D41_tiHhRwqA&amp;oe=6AB393CE; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/719160410_3377257819115289_4512916211874135718_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx960x720&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=kme4VsbYGiQQ7kNvwF0UTnh&amp;_nc_oc=AdpLFsFTOQlfY2GtWNtHZkgfNauVxu3L28i1m9bTX7UjZW46L_6uJXsumd63ry3hM_E&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIpFVodpDrLXaNrm03MWNxcRUQTUe0bD15QwfGTs15G_A&amp;oe=6AB39474; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715749899_3377270385780699_46444169963824531_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=m1B9Z9a3XTcQ7kNvwHbSueQ&amp;_nc_oc=AdqZvLfkUECCp-PzosWPpwH6aKcCTcnp5LCTlPaQnAapvNYk3h0vr0MwYZ74N6JJE60&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIIaHm-ZLLeWqyzE87P30_-cNCHO9sQVloN5bT3aFotpg&amp;oe=6AB395EC; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/720495745_3377270445780693_888169211609445957_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PEd1aWG90c4Q7kNvwFfUOQ4&amp;_nc_oc=AdrTRXfrx1pomRzcompzkQAMeyuhMDOb6GxUxdzedExILCEZNRNmCOswHKYdYi-vFpY&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQJdSmbYZUx1bo6s6BUqTCImTGV2rJasH5LeKQDXXFya1A&amp;oe=6AB3A127</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>83</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1763,43 +1853,44 @@
           <t>You guys were so helpful when I asked for advice so I thought I’d share a few of my “hacks” to maybe help someone else! ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>data\images\amazon_find_791791057\img_1.jpg; data\images\amazon_find_791791057\img_2.jpg; data\images\amazon_find_791791057\img_3.jpg; data\images\amazon_find_791791057\img_4.jpg</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Public Search</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>791791057</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/718204993_3377270389114032_3017451080494617445_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=qYfYw4OVFlQQ7kNvwFzTUw2&amp;_nc_oc=AdrTdokM1V_C9TzLfjq5_yhdW9z1pnNrXAPOqM7sMo9zBm1IgAoSMyik8zLi5QctYCQ&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQKN6mRZQV1JOvOk5cGH3-J9bLpZnNAF30D41_tiHhRwqA&amp;oe=6AB393CE; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/719160410_3377257819115289_4512916211874135718_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx960x720&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=kme4VsbYGiQQ7kNvwF0UTnh&amp;_nc_oc=AdpLFsFTOQlfY2GtWNtHZkgfNauVxu3L28i1m9bTX7UjZW46L_6uJXsumd63ry3hM_E&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIpFVodpDrLXaNrm03MWNxcRUQTUe0bD15QwfGTs15G_A&amp;oe=6AB39474; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/715749899_3377270385780699_46444169963824531_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=106&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=m1B9Z9a3XTcQ7kNvwHbSueQ&amp;_nc_oc=AdqZvLfkUECCp-PzosWPpwH6aKcCTcnp5LCTlPaQnAapvNYk3h0vr0MwYZ74N6JJE60&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQIIaHm-ZLLeWqyzE87P30_-cNCHO9sQVloN5bT3aFotpg&amp;oe=6AB395EC; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/720495745_3377270445780693_888169211609445957_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=PEd1aWG90c4Q7kNvwFfUOQ4&amp;_nc_oc=AdrTRXfrx1pomRzcompzkQAMeyuhMDOb6GxUxdzedExILCEZNRNmCOswHKYdYi-vFpY&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=MKX-JBaFHpnqnEGtSRwW4A&amp;_nc_ss=7b2a8&amp;oh=00_AQJdSmbYZUx1bo6s6BUqTCImTGV2rJasH5LeKQDXXFya1A&amp;oe=6AB3A127</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>91</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1829,41 +1920,47 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Honestly didn't expect rv stabilizer x chock to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>data\images\hack_3583318008493819\img_1.jpg; data\images\hack_3583318008493819\img_2.jpg; data\images\hack_3583318008493819\img_3.jpg</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>3583318008493819</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/763072132_10240527915834058_262860686266165320_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tQPKb_7z3scQ7kNvwHI1W7g&amp;_nc_oc=AdryOCOHLUetXqxLh_YB0dln50lhK5trI90T_Fm1qocc_zcSjKjM7rFYwajXvgsjhTI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJ0GnPf57poAwnS1tveFqIifG41xCwgcTXoj7nwXsPD0g&amp;oe=6AB39330; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/764719882_10240527916554076_6179174592261675065_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGePznIup-IQ7kNvwF8n1gs&amp;_nc_oc=AdpGktVoydqk0AxdQDAOzbx_Pf2MDjo3DIQObD1Zjm6Y7VQBbann44VUTt2JZv16NT8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJvlQLTekeLpX0VeuXsY7AW8BTlFEb4ontl07T28WmncA&amp;oe=6AB39768; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/762276276_10240527918834133_6935526286052437077_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=LUYt4ZPtFlQQ7kNvwFtDGTf&amp;_nc_oc=Ados7w7e5WTUF89zeazhrONFUSOjfR3KkU-WEt4FzNzv3RCM9gJpPLl89FV5RIzy0P4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQIUbRAOYKraspj5sBL0vF-0I_3MUiK5eLiusqFF-B6VQQ&amp;oe=6AB3908B</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>rv stabilizer x chock</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>83</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1893,43 +1990,50 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>If your RV rocks every time someone takes a single step inside, you need to try this.
+Our rig was perfectly level, but the floor still shook constantly. We tossed a set of X-chocks between the tires and it instantly locked everything solid. Worth every penny!
+I left the link in the first comment if you want to grab a pair 👇</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>data\images\hack_3583318008493819\img_1.jpg; data\images\hack_3583318008493819\img_2.jpg; data\images\hack_3583318008493819\img_3.jpg</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>3583318008493819</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/763072132_10240527915834058_262860686266165320_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tQPKb_7z3scQ7kNvwHI1W7g&amp;_nc_oc=AdryOCOHLUetXqxLh_YB0dln50lhK5trI90T_Fm1qocc_zcSjKjM7rFYwajXvgsjhTI&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJ0GnPf57poAwnS1tveFqIifG41xCwgcTXoj7nwXsPD0g&amp;oe=6AB39330; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/764719882_10240527916554076_6179174592261675065_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGePznIup-IQ7kNvwF8n1gs&amp;_nc_oc=AdpGktVoydqk0AxdQDAOzbx_Pf2MDjo3DIQObD1Zjm6Y7VQBbann44VUTt2JZv16NT8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQJvlQLTekeLpX0VeuXsY7AW8BTlFEb4ontl07T28WmncA&amp;oe=6AB39768; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/762276276_10240527918834133_6935526286052437077_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1152x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=LUYt4ZPtFlQQ7kNvwFtDGTf&amp;_nc_oc=Ados7w7e5WTUF89zeazhrONFUSOjfR3KkU-WEt4FzNzv3RCM9gJpPLl89FV5RIzy0P4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQIUbRAOYKraspj5sBL0vF-0I_3MUiK5eLiusqFF-B6VQQ&amp;oe=6AB3908B</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>rv stabilizer x chock</t>
         </is>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>83</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1956,41 +2060,42 @@
           <t>Hi all my husband and I bought our first ever brand new 2021 hideout! With one slideout! We bought it in April of this year! We were loving it so much, it was my dream ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_2519590198174784\img_1.jpg</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>2519590198174784</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/489965465_10161600930962880_4833098666534324521_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1504x2015&amp;ctp=p526x296&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=536f4a&amp;_nc_ohc=xMIVUG5htDkQ7kNvwG8ehE-&amp;_nc_oc=Adp4sJx_jBWQxqAezLmKNS9_5TDHX2yXRWxyb3DDrZ3-anVVRKHC96Jtv_1gNntBUhE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKdYBPNRTeYp1FOp6-rBTffCUwYr55-PcsfEHer1NRGrw&amp;oe=6AB3994F</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2017,43 +2122,44 @@
           <t>Hi all my husband and I bought our first ever brand new 2021 hideout! With one slideout! We bought it in April of this year! We were loving it so much, it was my dream ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_2519590198174784\img_1.jpg</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>2519590198174784</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/489965465_10161600930962880_4833098666534324521_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1504x2015&amp;ctp=p526x296&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=536f4a&amp;_nc_ohc=xMIVUG5htDkQ7kNvwG8ehE-&amp;_nc_oc=Adp4sJx_jBWQxqAezLmKNS9_5TDHX2yXRWxyb3DDrZ3-anVVRKHC96Jtv_1gNntBUhE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKdYBPNRTeYp1FOp6-rBTffCUwYr55-PcsfEHer1NRGrw&amp;oe=6AB3994F</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>89</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2086,41 +2192,47 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Honestly didn't expect rv small dehumidifier to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>data\images\hack_3513687305456890\img_1.jpg; data\images\hack_3513687305456890\img_2.jpg</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>3513687305456890</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>rv small dehumidifier</t>
         </is>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>70</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2153,43 +2265,49 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Honestly didn't expect rv small dehumidifier to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>data\images\hack_3513687305456890\img_1.jpg; data\images\hack_3513687305456890\img_2.jpg</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>3513687305456890</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/711643338_4031111337187636_2883491981945560264_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx2048x1536&amp;ctp=s590x590&amp;_nc_cat=101&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=f_dNgnnJOYgQ7kNvwExjlSF&amp;_nc_oc=AdrWkULW0up9vpUlFyOdOOVFswpvqlDIhNLfoyhWvHBlMRRjGZi30e5xunQe5kh6Z0Q&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQKTSnMNFsMvYlBm6Q9Cs_j26ctmUP0uKKMt38ogPK1CCQ&amp;oe=6AB3BE3A; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/710079281_4031111510520952_7622572342432142030_n.jpg?stp=cp6_dst-jpegr_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=4dRi6V0TjK4Q7kNvwHSnOiX&amp;_nc_oc=AdrDAS7dm4zU-dcnhVK6W-knhBbh3pssG6jJndvEsBOKEvFfAFNNPsyLOvKMWjs_ivI&amp;_nc_zt=23&amp;se=-1&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=ViAqpShX1Nm9L2g-4A-cEw&amp;_nc_ss=7b2a8&amp;oh=00_AQI6pqkPWZ9WIOjSIkSrF2puVgdYZN4nCE9eR76sArCmFA&amp;oe=6AB3B093</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>rv small dehumidifier</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>70</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2221,43 +2339,51 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Almost had a heart attack when my toddler opened our RV door in the middle of the night.
+Standard locks weren't cutting it, but this cheap Amazon safety lock mounts up high with zero drilling required.
+Now I can actually sleep soundly on our trips! 
+I left the link in the first comment 👇</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>data\images\amazon_find_2956335967833536\img_1.jpg</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>2956335967833536</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/486263063_3431305033666747_2774947844339664550_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_V3lAOuS71gQ7kNvwG1HA6t&amp;_nc_oc=Ado0M-qFkVhQnVlLURz25aP5SNH_jAdpe4Dmc4HtVTUByPMy0vPdcFtq1ganZeRHiEc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQK8ZOwXZcwYIiJ5OsCjs7fTQm9bTUEleRwYHx_4DZJBiw&amp;oe=6AB39B39</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>إكسسوارات وأدوات تجارية (Commercial Gear &amp; Accessories)</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>81</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2287,43 +2413,44 @@
 Any suggestions on good locks? ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>data\images\amazon_find_2956335967833536\img_1.jpg</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>2956335967833536</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/486263063_3431305033666747_2774947844339664550_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=_V3lAOuS71gQ7kNvwG1HA6t&amp;_nc_oc=Ado0M-qFkVhQnVlLURz25aP5SNH_jAdpe4Dmc4HtVTUByPMy0vPdcFtq1ganZeRHiEc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQK8ZOwXZcwYIiJ5OsCjs7fTQm9bTUEleRwYHx_4DZJBiw&amp;oe=6AB39B39</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>إكسسوارات وحلول ذكية (Smart Accessories &amp; Hacks)</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>81</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2351,39 +2478,40 @@
 On our first trip, the slide out wouldn’t retract all the way on its own (yes, I checked it prior to purchase and it seemed to work fine, but looking back, I think they had it jacked up on that side to help assist it and I just thought the driveway was pitched). It would get about a foot out and come to a stop. If I had it jacked up slightly and leaned into it, I ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
         <is>
           <t>data\images\recommendation_4219763604824093\img_1.jpg</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4219763604824093</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2411,41 +2539,42 @@
 On our first trip, the slide out wouldn’t retract all the way on its own (yes, I checked it prior to purchase and it seemed to work fine, but looking back, I think they had it jacked up on that side to help assist it and I just thought the driveway was pitched). It would get about a foot out and come to a stop. If I had it jacked up slightly and leaned into it, I ... عرض المزيد</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>data\images\recommendation_4219763604824093\img_1.jpg</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>4219763604824093</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/778928638_10234377270479258_6720371812830267357_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x773&amp;ctp=p180x540&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=2MFpcUQX5nAQ7kNvwGeefCS&amp;_nc_oc=AdpY7NG2vbXAeZdlBhdLZ0XnO1G2KpbNq-q-Vi50uubkYztx7ASFIj4MVK_Shql8qB8&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=A8Me3j8jNja1Mkq3I5rYPg&amp;_nc_ss=7b2a8&amp;oh=00_AQJ-yYB_jczpZmho-tcYD7J0ValNk1dW5sFyRVmDscJnXQ&amp;oe=6AB396CA</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2474,43 +2603,51 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>If your stinky slinky won’t fit inside your RV bumper, stop forcing it. 
+I got tired of wrestling mine and grabbed this under-rig storage tube on Amazon. 
+Fits the thick fittings easily and mounts right to the frame in 10 minutes. 
+Left the link in the comments if you need one! 👇</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>data\images\amazon_find_4228244110642709\img_1.jpg</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>4228244110642709</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/789447152_10244813111573647_47739271540443468_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx720x1280&amp;ctp=p526x296&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9RQ21jppgcUQ7kNvwHOPHq-&amp;_nc_oc=AdpS_m5-K5_RU2sUwoQJWJrY-sl4KHrcU30zbIzSrUQ3R25NJhL2uHJx88ZWQYW0umU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKmJVCGhzzaIOrLJSB17QoEwCChxJioCHSDOxuyqiFvMA&amp;oe=6AB3A606</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>تنظيم وتخزين جاهز (Storage &amp; Organization)</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>81</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2537,43 +2674,44 @@
           <t>My stinky slinky won’t fit in the bumper tubing. Any ideas?</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
         <is>
           <t>data\images\amazon_find_4228244110642709\img_1.jpg</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>4228244110642709</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/789447152_10244813111573647_47739271540443468_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx720x1280&amp;ctp=p526x296&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9RQ21jppgcUQ7kNvwHOPHq-&amp;_nc_oc=AdpS_m5-K5_RU2sUwoQJWJrY-sl4KHrcU30zbIzSrUQ3R25NJhL2uHJx88ZWQYW0umU&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKmJVCGhzzaIOrLJSB17QoEwCChxJioCHSDOxuyqiFvMA&amp;oe=6AB3A606</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>تنظيم وتخزين (Storage &amp; Organization)</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>rv amazon find</t>
         </is>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>81</v>
       </c>
-      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2600,41 +2738,42 @@
           <t>Soo I want to paint the walls in my camper and I was wondering is there a certain paint or way to go about doing this? Below is what my walls look like in my camper.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_3605957036204756\img_1.jpg</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>3605957036204756</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/514417036_24232386396387276_8898425086872934580_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=0WuEyVKJSqkQ7kNvwGxzTrJ&amp;_nc_oc=AdpwYEulmgEEsjJgMkkuOg0h0LPQX5Bi_s7roUkZ1JKXJsLZhWL2MrHLy_UyPk1-mPA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKl3JPpvV7FsczmsCXiMGk3JcjuvjpM0ztQZBAozZpITg&amp;oe=6AB3CB59</t>
         </is>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2661,43 +2800,44 @@
           <t>Soo I want to paint the walls in my camper and I was wondering is there a certain paint or way to go about doing this? Below is what my walls look like in my camper.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
         <is>
           <t>data\images\must_have_gadget_3605957036204756\img_1.jpg</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>3605957036204756</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/514417036_24232386396387276_8898425086872934580_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=p526x296&amp;_nc_cat=111&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=0WuEyVKJSqkQ7kNvwGxzTrJ&amp;_nc_oc=AdpwYEulmgEEsjJgMkkuOg0h0LPQX5Bi_s7roUkZ1JKXJsLZhWL2MrHLy_UyPk1-mPA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=xdIPSj7R-3lhEMKdb3QlGQ&amp;_nc_ss=7b2a8&amp;oh=00_AQKl3JPpvV7FsczmsCXiMGk3JcjuvjpM0ztQZBAozZpITg&amp;oe=6AB3CB59</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>1</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>rv must have gadget</t>
         </is>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>81</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2726,29 +2866,30 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>4242996285834158</v>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2777,31 +2918,32 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>4242996285834158</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2830,31 +2972,32 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>3581840501974903</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2883,21 +3026,22 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>3581840501974903</v>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2926,29 +3070,30 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>4244102009056919</v>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2977,31 +3122,32 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>4244102009056919</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3030,31 +3176,32 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>3622362671256019</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3083,21 +3230,22 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>3622362671256019</v>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3124,39 +3272,40 @@
           <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
         <is>
           <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>3628769393948680</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
         </is>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>غير مؤكد (نقاش عام)</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3183,41 +3332,42 @@
           <t>My motor home is five years old and the fiberglass is getting a little dull. I would appreciate recommendations for a product that will remove the oxidation, give it some shine, and not damage the vinyl graphics. Preferably a product that will be kind to 72 year old shoulders and not break the bank. Am I asking too much?</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
         <is>
           <t>data\images\recommendation_3628769393948680\img_1.jpg</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>3628769393948680</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/808052775_10215713116376802_6417467035183016827_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx2048x1536&amp;ctp=s720x720&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=5aeIRrCJGp4Q7kNvwHvDyKy&amp;_nc_oc=AdqG_YVwrxVe6Fyw0hKRqTYuhf09LUF3aWqDHRgNV4bC3Ywaab_Alz2SaleHUdgWCOA&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=vfknkuq86QfA8Lw-aBT1Xw&amp;_nc_ss=7b2a8&amp;oh=00_AQKVtcAXNMkkVDiI2ToSgwRqlB1V4TAv598oTL1uJTj_nw&amp;oe=6AB3A6DD</t>
         </is>
       </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>غير مؤكد (نقاش عام)</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3247,31 +3397,32 @@
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>3218284608305336</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3301,143 +3452,151 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>3218284608305336</v>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>amazon find</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>8</v>
       </c>
       <c r="C48" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
+          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>roadtreking</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>3359003754258580</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Honestly didn't expect rv 12v portable bunk fan to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>data\images\amazon_find_4147910648676056\img_1.jpg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>RVhackcamp</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>4147910648676056</v>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>غير مؤهل (بدون صور)</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKuI7NhSiWUW3pweIYcuSccGm2fBiXhQmnukqpjQKDiRg&amp;oe=6AB3C7D6</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>rv 12v portable bunk fan</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>81</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>8</v>
       </c>
       <c r="C49" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/RVhackcamp/posts/4147910648676056/</t>
+          <t>https://www.facebook.com/groups/roadtreking/posts/3359003754258580/</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Does anyone have a hack for cooling the bottom bunk better? We’ve tried mini fans but they don’t seem to stay upright or stick to the walls very well. I wish we could get an ac vent in there!</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>data\images\hack_4147910648676056\img_1.jpg</t>
-        </is>
-      </c>
+          <t>Looking for recommendation on the best route (east to west) through Dallas /Ft Worth.   Midweek, hitting Dallas around Noon.  Pulling 36ft 5th wheel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>RVhackcamp</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>4147910648676056</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=05iOM0uUuQJ8MOIbywV40A&amp;_nc_ss=7b2a8&amp;oh=00_AQJbpgw45n6W01WKIaXHwonMf_0WGJsRiKeyxgsMLPAUaA&amp;oe=6AB3C7D6</t>
-        </is>
-      </c>
-      <c r="M49" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>أجهزة وإلكترونيات (Gadgets &amp; Power)</t>
-        </is>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>roadtreking</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>3359003754258580</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>0</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>rv 12v portable bunk fan</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+          <t>غير مؤهل (بدون صور)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3466,43 +3625,50 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>The bottom RV bunk used to be an absolute sauna until I found this on Amazon.
+Regular mini fans kept falling off, but this 12V fan clips on tight and actually pushes real air into that stuffy corner. My kids finally slept through the night!
+I'll drop the link in the first comment 👇</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>data\images\amazon_find_4147910648676056\img_1.jpg</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>4147910648676056</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/730771479_10102373262656439_2111230534189182674_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1206x952&amp;ctp=s640x640&amp;_nc_cat=107&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=DGSaV9gAmTAQ7kNvwEywMS_&amp;_nc_oc=AdprvPdL0g_5W2xgZVeuTA___ucidu0kEo0UPwtfNjLrGr8lzJOIt34RmN_8IoOdX94&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=-DNXGqSwxAYHz3InfHrB2g&amp;_nc_ss=7b2a8&amp;oh=00_AQKuI7NhSiWUW3pweIYcuSccGm2fBiXhQmnukqpjQKDiRg&amp;oe=6AB3C7D6</t>
         </is>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>1</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>rv 12v portable bunk fan</t>
         </is>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>81</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3531,31 +3697,32 @@
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>3359003754258580</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3586,29 +3753,30 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>3629156827243270</v>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr">
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3639,31 +3807,32 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>3629156827243270</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr">
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3692,29 +3861,30 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>3128604820606649</v>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3743,29 +3913,30 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>3617867058372247</v>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3794,31 +3965,32 @@
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>3617867058372247</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr">
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3847,31 +4019,32 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>3128604820606649</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr">
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3900,31 +4073,32 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>3631536470338639</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr">
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3953,29 +4127,30 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>3631536470338639</v>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr">
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>غير مؤهل (بدون صور)</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4003,39 +4178,40 @@
 Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
         <is>
           <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>2790989414393353</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
         </is>
       </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4063,41 +4239,42 @@
 Update: You all brought up a good question about draining the pool if it’s covering the shower drain. I’ve got a piece of 1” pvc pipe that’s about 18” long that I’m going to lay under it. Facing from the pool drain to the shower drain under the pool. I’m camping this week, so I’ll see how it goes.</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
         <is>
           <t>data\images\hack_2790989414393353\img_1.jpg; data\images\hack_2790989414393353\img_2.jpg</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>2790989414393353</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516090961_10161909893284624_6283109645827272953_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=21QqBNNBMMcQ7kNvwFXmmny&amp;_nc_oc=AdrIEx__5typW7hR-DVpS1cS1KiVvk1PrfvUy26A3MGBEJcLOT0Oz5h4wAD_aTiMtdc&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLgKymahQgQWWDKDwUd5LluEkBVgZe5TCVyySuErcYTww&amp;oe=6AB39D03; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/516439294_10161909893409624_2902390173952908189_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx720x960&amp;ctp=s590x590&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=9TTZG7uN0nkQ7kNvwFOhIIY&amp;_nc_oc=AdqP8y920xXQBZnI0FoR2RcYpOQMVJtpls36tvoc7d_cT6Xch6Ir9FtebeM4WsSVGNo&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQIV_O5dGMlir-2F0tzLrKDH1Pb9-zFmXcRrhC7qYi-1pA&amp;oe=6AB392A5</t>
         </is>
       </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4124,41 +4301,42 @@
           <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
         <is>
           <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>3498835016916959</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
         </is>
       </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
         <is>
           <t>استبعاد (نقاش/سفر/شكوى)</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4185,31 +4363,32 @@
           <t>Ok, maybe others have already done this but this was an inspiration my husband had for our new Class C. There is a stairwell that we worried we (or the dogs) would accidentally fall into. My hubby came up with this idea, I came up with the suggestion to staple one of Costco's rugs on it. To finish it off, so it could be easily moved aside, he attached handles and then screwed 2"x1" wood on the underside so it wouldn't move. I told him that he is brilliant! About a $33 project... عرض المزيد</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
         <is>
           <t>data\images\hack_3498835016916959\img_1.jpg; data\images\hack_3498835016916959\img_2.jpg; data\images\hack_3498835016916959\img_3.jpg</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
         <is>
           <t>RVhackcamp</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>3498835016916959</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/654206606_10233790263479320_8934352753678604081_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1186x843&amp;ctp=p417x417&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=6LvqWaRXDpoQ7kNvwHwFbcw&amp;_nc_oc=AdpRHF1lFIaB6-KwLOaxGwdKgH_HBUhvMtjzs-KH2Fc75eNwZYiKzaBQflOJ5FeGvI0&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIsssXBVDsOtyPFbNnElRdrLu2szoLm7n1qTPnGMyvooQ&amp;oe=6AB3B55E; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/655884715_10233790268919456_2843537399331144636_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx881x828&amp;ctp=s590x590&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=tPEB8O9Kw8UQ7kNvwFZuVrV&amp;_nc_oc=AdqAr-YgIDyEtHOAEil6jSOgzA2VEFa-92RlVgLgi7BKPLYtkCurMvVl2nGViUNM7M4&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIBieMdP15PfKQduK69kUkbIFthgt7oxQbZQJL2jWTmtw&amp;oe=6AB3A6A8; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/653720541_10233790263119311_2765445185799412382_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1204x904&amp;ctp=s590x590&amp;_nc_cat=108&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=oM21kLkiyXsQ7kNvwHrlGX5&amp;_nc_oc=AdosGU9wVGu-J4ks1YaFDknSu9pyGkNeKJ24PaDuDenJJ36LrD7FMNKTAobtawAnt7s&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=exjfy8yYqfVcO20J6DAxdQ&amp;_nc_ss=7b2a8&amp;oh=00_AQIERMSv9kKcWTY3PqqYJGPNgZ1dVK1fXzhW1DkB8pjJmg&amp;oe=6AB3C373</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4238,41 +4417,47 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>Honestly didn't expect tailgate jack clearance flip to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>3080238785468413</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
         </is>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>1</v>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>tailgate jack clearance flip</t>
         </is>
       </c>
-      <c r="P64" t="n">
+      <c r="Q64" t="n">
         <v>70</v>
       </c>
-      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4301,43 +4486,49 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>Honestly didn't expect tailgate jack clearance flip to work this well, but it literally solved the problem on our last trip! Best purchase I've made in a while.
+I left the direct link in the first comment for anyone who needs it 👇</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>data\images\hack_3080238785468413\img_1.jpg; data\images\hack_3080238785468413\img_2.jpg</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
         <is>
           <t>roadtreking</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>3080238785468413</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
         <is>
           <t>https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500430078_3841916402724353_3119412760577639463_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=103&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=3xqMlISBjIAQ7kNvwENGyA2&amp;_nc_oc=AdphwVhDvgBsBIiUyBGAqFab8JKFEBl-ecLqi4_6rvPomUH0laWqxzUXvA0Hp3F6cnE&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQJiTLsbWgMHnDbD8AoTrKPQhartpGy2zgjUopRGh1QFmg&amp;oe=6AB3AAA4; https://scontent.fcai19-4.fna.fbcdn.net/v/t39.30808-6/500048722_3841913929391267_3300619833621540495_n.jpg?stp=cp6_dst-jpg_tt6&amp;cstp=mx1536x2048&amp;ctp=s590x590&amp;_nc_cat=109&amp;_nc_map=urlgen_bucketless&amp;ccb=1-7&amp;_nc_sid=aa7b47&amp;_nc_ohc=-2TDJzpVcRAQ7kNvwFQnEva&amp;_nc_oc=AdpuXbdoq6LmiDAsXAmE89aFLUFHh2e5Fc4jb6FbXJLqE7s22JgyrfFYcSRJWFlKx7w&amp;_nc_zt=23&amp;_nc_ht=scontent.fcai19-4.fna&amp;_nc_gid=TuN4VeIUhMEDbkGyUlP9RA&amp;_nc_ss=7b2a8&amp;oh=00_AQLiyUu5lHeDHBi0WUR9hqUc5La82DyJVCGYjRR9HpYQxg&amp;oe=6AB3AB49</t>
         </is>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>1</v>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>أجهزة وإلكترونيات استهلاكية (Gadgets &amp; Appliances)</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>tailgate jack clearance flip</t>
         </is>
       </c>
-      <c r="P65" t="n">
+      <c r="Q65" t="n">
         <v>70</v>
       </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
